--- a/woocommerce/suppliers/jewellery/stock_sheet.xlsx
+++ b/woocommerce/suppliers/jewellery/stock_sheet.xlsx
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S143"/>
+  <dimension ref="A1:S150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -657,24 +657,24 @@
       <c r="A3" s="3" t="inlineStr"/>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>F02243</t>
+          <t>LSL</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>9808</t>
+          <t>15503</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr"/>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Mobile &amp; Jewellery Precision 5 Piece Screwdriver Set</t>
+          <t>50m LED String Lights - TYN-060- all colors</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr"/>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>All Products</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr"/>
@@ -687,7 +687,7 @@
         <v/>
       </c>
       <c r="L3" s="9" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="M3" s="10">
         <f>IF(OR(L3="",K3="",L3=0),"",
@@ -697,11 +697,7 @@
       <c r="N3" s="11" t="inlineStr"/>
       <c r="O3" s="4" t="inlineStr"/>
       <c r="P3" s="4" t="inlineStr"/>
-      <c r="Q3" s="4" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/03/IMG_7055.jpg</t>
-        </is>
-      </c>
+      <c r="Q3" s="4" t="inlineStr"/>
       <c r="R3" s="4" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -709,7 +705,7 @@
       </c>
       <c r="S3" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -717,24 +713,24 @@
       <c r="A4" s="3" t="inlineStr"/>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>F00940-01</t>
+          <t>2BOFU12961</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>12961</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr"/>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>Alco Measuring Tape Plastic</t>
+          <t>7N007 Dreamcatcher Sterling Silver CZ Pendant And Chain</t>
         </is>
       </c>
       <c r="F4" s="12" t="inlineStr"/>
       <c r="G4" s="12" t="inlineStr">
         <is>
-          <t>All Products</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H4" s="12" t="inlineStr"/>
@@ -746,7 +742,9 @@
         <f>IF(I4="","",I4*(1+J4/100))</f>
         <v/>
       </c>
-      <c r="L4" s="6" t="inlineStr"/>
+      <c r="L4" s="13" t="n">
+        <v>350</v>
+      </c>
       <c r="M4" s="10">
         <f>IF(OR(L4="",K4="",L4=0),"",
   (L4-K4)/L4*100)</f>
@@ -755,11 +753,7 @@
       <c r="N4" s="11" t="inlineStr"/>
       <c r="O4" s="12" t="inlineStr"/>
       <c r="P4" s="12" t="inlineStr"/>
-      <c r="Q4" s="12" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/03/IMG_7063.jpg</t>
-        </is>
-      </c>
+      <c r="Q4" s="12" t="inlineStr"/>
       <c r="R4" s="12" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -767,7 +761,7 @@
       </c>
       <c r="S4" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -775,24 +769,24 @@
       <c r="A5" s="3" t="inlineStr"/>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>9902054073171</t>
+          <t>F00940-01</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>9975</t>
+          <t>9974</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr"/>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Alco Measuring Tape Rubber</t>
+          <t>Alco Measuring Tape Plastic</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>All Products</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
@@ -813,11 +807,7 @@
       <c r="N5" s="11" t="inlineStr"/>
       <c r="O5" s="4" t="inlineStr"/>
       <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/03/IMG_7062.jpg</t>
-        </is>
-      </c>
+      <c r="Q5" s="4" t="inlineStr"/>
       <c r="R5" s="4" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -825,7 +815,7 @@
       </c>
       <c r="S5" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -833,24 +823,24 @@
       <c r="A6" s="3" t="inlineStr"/>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>9902054073263</t>
+          <t>F00942</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>9984</t>
+          <t>18426</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr"/>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Alco Spring Hammer Forged</t>
+          <t>Alco Measuring Tape Plastic - 10m</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr"/>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>All Products</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr"/>
@@ -863,7 +853,7 @@
         <v/>
       </c>
       <c r="L6" s="13" t="n">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="M6" s="10">
         <f>IF(OR(L6="",K6="",L6=0),"",
@@ -873,11 +863,7 @@
       <c r="N6" s="11" t="inlineStr"/>
       <c r="O6" s="12" t="inlineStr"/>
       <c r="P6" s="12" t="inlineStr"/>
-      <c r="Q6" s="12" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/03/IMG_7074.jpg</t>
-        </is>
-      </c>
+      <c r="Q6" s="12" t="inlineStr"/>
       <c r="R6" s="12" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -885,7 +871,7 @@
       </c>
       <c r="S6" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -893,24 +879,24 @@
       <c r="A7" s="3" t="inlineStr"/>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>ME-650-VU</t>
+          <t>F00940</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>11830</t>
+          <t>18428</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr"/>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Mecer UPS with AVR,Monitoring Software + Cable &amp; Built-in Surge Protection</t>
+          <t>Alco Measuring Tape Plastic - 3m</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>All Products</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
@@ -922,7 +908,9 @@
         <f>IF(I7="","",I7*(1+J7/100))</f>
         <v/>
       </c>
-      <c r="L7" s="6" t="inlineStr"/>
+      <c r="L7" s="9" t="n">
+        <v>140</v>
+      </c>
       <c r="M7" s="10">
         <f>IF(OR(L7="",K7="",L7=0),"",
   (L7-K7)/L7*100)</f>
@@ -931,11 +919,7 @@
       <c r="N7" s="11" t="inlineStr"/>
       <c r="O7" s="4" t="inlineStr"/>
       <c r="P7" s="4" t="inlineStr"/>
-      <c r="Q7" s="4" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/05/Mecer-1000VA-600W-OFFLINE-UPS-510x510-1.jpg, https://happyharvesting.co.za/wp-content/uploads/2023/05/41XQC9Fo1cL._AC_.jpg, https://happyharvesting.co.za/wp-content/uploads/2023/05/36871310-pdpxl-300x300-2.jpg</t>
-        </is>
-      </c>
+      <c r="Q7" s="4" t="inlineStr"/>
       <c r="R7" s="4" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -943,7 +927,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -951,22 +935,26 @@
       <c r="A8" s="3" t="inlineStr"/>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>ME-650-VU-01</t>
+          <t>F00941</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>11838</t>
+          <t>18427</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr"/>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>Mecer UPS with AVR,Monitoring Software + Cable &amp; Built-in Surge Protection - ME-850-VU Mecer 850VA / 480W OFF-LINE UPS</t>
+          <t>Alco Measuring Tape Plastic - 5m</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr"/>
-      <c r="G8" s="12" t="inlineStr"/>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
       <c r="H8" s="12" t="inlineStr"/>
       <c r="I8" s="6" t="inlineStr"/>
       <c r="J8" s="7" t="n">
@@ -977,7 +965,7 @@
         <v/>
       </c>
       <c r="L8" s="13" t="n">
-        <v>1900</v>
+        <v>150</v>
       </c>
       <c r="M8" s="10">
         <f>IF(OR(L8="",K8="",L8=0),"",
@@ -995,7 +983,7 @@
       </c>
       <c r="S8" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -1003,22 +991,26 @@
       <c r="A9" s="3" t="inlineStr"/>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>ME-650-VU-02</t>
+          <t>9902054073171</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>11839</t>
+          <t>9975</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr"/>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Mecer UPS with AVR,Monitoring Software + Cable &amp; Built-in Surge Protection - ME-1000-VU Mecer 1000VA / 600W OFF-LINE UPS</t>
+          <t>Alco Measuring Tape Rubber</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
       <c r="H9" s="4" t="inlineStr"/>
       <c r="I9" s="6" t="inlineStr"/>
       <c r="J9" s="7" t="n">
@@ -1028,9 +1020,7 @@
         <f>IF(I9="","",I9*(1+J9/100))</f>
         <v/>
       </c>
-      <c r="L9" s="9" t="n">
-        <v>2100</v>
-      </c>
+      <c r="L9" s="6" t="inlineStr"/>
       <c r="M9" s="10">
         <f>IF(OR(L9="",K9="",L9=0),"",
   (L9-K9)/L9*100)</f>
@@ -1047,7 +1037,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -1055,22 +1045,26 @@
       <c r="A10" s="3" t="inlineStr"/>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>ME-650-VU-03</t>
+          <t>F00945</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>11840</t>
+          <t>18421</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr"/>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>Mecer UPS with AVR,Monitoring Software + Cable &amp; Built-in Surge Protection - ME-2000-VU Mecer 2000VA / 1200W OFF-LINE UPS</t>
+          <t>Alco Measuring Tape Rubber - 10m</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr"/>
-      <c r="G10" s="12" t="inlineStr"/>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
       <c r="H10" s="12" t="inlineStr"/>
       <c r="I10" s="6" t="inlineStr"/>
       <c r="J10" s="7" t="n">
@@ -1081,7 +1075,7 @@
         <v/>
       </c>
       <c r="L10" s="13" t="n">
-        <v>3000</v>
+        <v>190</v>
       </c>
       <c r="M10" s="10">
         <f>IF(OR(L10="",K10="",L10=0),"",
@@ -1099,7 +1093,7 @@
       </c>
       <c r="S10" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -1107,22 +1101,26 @@
       <c r="A11" s="3" t="inlineStr"/>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>ME-650-VU-04</t>
+          <t>F00943</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>11841</t>
+          <t>18424</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr"/>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Mecer UPS with AVR,Monitoring Software + Cable &amp; Built-in Surge Protection - ME-3000-VU+ Mecer 3000VA / 1800W OFF-LINE UPS</t>
+          <t>Alco Measuring Tape Rubber - 3m</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
       <c r="H11" s="4" t="inlineStr"/>
       <c r="I11" s="6" t="inlineStr"/>
       <c r="J11" s="7" t="n">
@@ -1133,7 +1131,7 @@
         <v/>
       </c>
       <c r="L11" s="9" t="n">
-        <v>5450</v>
+        <v>160</v>
       </c>
       <c r="M11" s="10">
         <f>IF(OR(L11="",K11="",L11=0),"",
@@ -1151,7 +1149,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -1159,22 +1157,26 @@
       <c r="A12" s="3" t="inlineStr"/>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>ME-650-VU-05</t>
+          <t>F00944</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>11842</t>
+          <t>18423</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr"/>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>Mecer UPS with AVR,Monitoring Software + Cable &amp; Built-in Surge Protection - ME-1000-WPTU+ Mecer 1000VA / 800W ON-LINE UPS</t>
+          <t>Alco Measuring Tape Rubber - 5m</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr"/>
-      <c r="G12" s="12" t="inlineStr"/>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
       <c r="H12" s="12" t="inlineStr"/>
       <c r="I12" s="6" t="inlineStr"/>
       <c r="J12" s="7" t="n">
@@ -1185,7 +1187,7 @@
         <v/>
       </c>
       <c r="L12" s="13" t="n">
-        <v>4550</v>
+        <v>170</v>
       </c>
       <c r="M12" s="10">
         <f>IF(OR(L12="",K12="",L12=0),"",
@@ -1203,7 +1205,7 @@
       </c>
       <c r="S12" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -1211,22 +1213,26 @@
       <c r="A13" s="3" t="inlineStr"/>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>ME-650-VU-06</t>
+          <t>F02210</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>11843</t>
+          <t>18422</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr"/>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Mecer UPS with AVR,Monitoring Software + Cable &amp; Built-in Surge Protection - ME-2000-WPTU+ Mecer 2000VA / 1600W ON-LINE UPS</t>
+          <t>Alco Measuring Tape Rubber - 7.5m</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr"/>
-      <c r="G13" s="4" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
       <c r="H13" s="4" t="inlineStr"/>
       <c r="I13" s="6" t="inlineStr"/>
       <c r="J13" s="7" t="n">
@@ -1237,7 +1243,7 @@
         <v/>
       </c>
       <c r="L13" s="9" t="n">
-        <v>7350</v>
+        <v>180</v>
       </c>
       <c r="M13" s="10">
         <f>IF(OR(L13="",K13="",L13=0),"",
@@ -1255,7 +1261,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -1263,22 +1269,26 @@
       <c r="A14" s="3" t="inlineStr"/>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>ME-650-VU-07</t>
+          <t>9902054073263</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>11844</t>
+          <t>9984</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr"/>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>Mecer UPS with AVR,Monitoring Software + Cable &amp; Built-in Surge Protection - ME-3000-WPTV Mecer 3000VA / 2700W ON-LINE UPS</t>
+          <t>Alco Spring Hammer Forged</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr"/>
-      <c r="G14" s="12" t="inlineStr"/>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
       <c r="H14" s="12" t="inlineStr"/>
       <c r="I14" s="6" t="inlineStr"/>
       <c r="J14" s="7" t="n">
@@ -1289,7 +1299,7 @@
         <v/>
       </c>
       <c r="L14" s="13" t="n">
-        <v>10650</v>
+        <v>250</v>
       </c>
       <c r="M14" s="10">
         <f>IF(OR(L14="",K14="",L14=0),"",
@@ -1307,7 +1317,7 @@
       </c>
       <c r="S14" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -1315,22 +1325,26 @@
       <c r="A15" s="3" t="inlineStr"/>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>ME-650-VU-08</t>
+          <t>F02251</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>11845</t>
+          <t>32245</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr"/>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Mecer UPS with AVR,Monitoring Software + Cable &amp; Built-in Surge Protection - ME-6000-WPTV Mecer 6000VA / 6000W ON-LINE UPS</t>
+          <t>Catering Table - Black</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr"/>
-      <c r="G15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
       <c r="H15" s="4" t="inlineStr"/>
       <c r="I15" s="6" t="inlineStr"/>
       <c r="J15" s="7" t="n">
@@ -1340,9 +1354,7 @@
         <f>IF(I15="","",I15*(1+J15/100))</f>
         <v/>
       </c>
-      <c r="L15" s="9" t="n">
-        <v>19900</v>
-      </c>
+      <c r="L15" s="6" t="inlineStr"/>
       <c r="M15" s="10">
         <f>IF(OR(L15="",K15="",L15=0),"",
   (L15-K15)/L15*100)</f>
@@ -1359,7 +1371,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -1367,22 +1379,26 @@
       <c r="A16" s="3" t="inlineStr"/>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>ME-650-VU-09</t>
+          <t>F00417</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>11846</t>
+          <t>32248</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr"/>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>Mecer UPS with AVR,Monitoring Software + Cable &amp; Built-in Surge Protection - ME-10000-WPTV Mecer 10000VA / 10000W ON-LINE UPS</t>
+          <t>Catering Table - White</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr"/>
-      <c r="G16" s="12" t="inlineStr"/>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
       <c r="H16" s="12" t="inlineStr"/>
       <c r="I16" s="6" t="inlineStr"/>
       <c r="J16" s="7" t="n">
@@ -1393,7 +1409,7 @@
         <v/>
       </c>
       <c r="L16" s="13" t="n">
-        <v>22500</v>
+        <v>399</v>
       </c>
       <c r="M16" s="10">
         <f>IF(OR(L16="",K16="",L16=0),"",
@@ -1411,7 +1427,7 @@
       </c>
       <c r="S16" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -1419,22 +1435,26 @@
       <c r="A17" s="3" t="inlineStr"/>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>ME-650-VU-10</t>
+          <t>SOZXJ13430</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>11975</t>
+          <t>13430</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr"/>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Mecer UPS with AVR,Monitoring Software + Cable &amp; Built-in Surge Protection - ME-650-VU 650VA OFF-LINE UPS</t>
+          <t>Cream Chiffon Stud &amp; Stone Detail Dress</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr"/>
-      <c r="G17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
       <c r="H17" s="4" t="inlineStr"/>
       <c r="I17" s="6" t="inlineStr"/>
       <c r="J17" s="7" t="n">
@@ -1445,7 +1465,7 @@
         <v/>
       </c>
       <c r="L17" s="9" t="n">
-        <v>1300</v>
+        <v>600</v>
       </c>
       <c r="M17" s="10">
         <f>IF(OR(L17="",K17="",L17=0),"",
@@ -1463,7 +1483,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -1471,24 +1491,24 @@
       <c r="A18" s="3" t="inlineStr"/>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>ELTW712254</t>
+          <t>6A1AU12978</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>12254</t>
+          <t>12978</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr"/>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Lightweight Jacket/Coat Sequin and Drawstring</t>
+          <t>ER003 Sterling Silver Cluster CZ Hoop Earrings</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr"/>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>Lifestyle &amp; Everyday Essentials &gt; Fashion</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H18" s="12" t="inlineStr"/>
@@ -1500,7 +1520,9 @@
         <f>IF(I18="","",I18*(1+J18/100))</f>
         <v/>
       </c>
-      <c r="L18" s="6" t="inlineStr"/>
+      <c r="L18" s="13" t="n">
+        <v>280</v>
+      </c>
       <c r="M18" s="10">
         <f>IF(OR(L18="",K18="",L18=0),"",
   (L18-K18)/L18*100)</f>
@@ -1509,11 +1531,7 @@
       <c r="N18" s="11" t="inlineStr"/>
       <c r="O18" s="12" t="inlineStr"/>
       <c r="P18" s="12" t="inlineStr"/>
-      <c r="Q18" s="12" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/05/IMG-20230428-WA0124-removebg-preview.png, https://happyharvesting.co.za/wp-content/uploads/2023/05/IMG-20230428-WA0122.jpg</t>
-        </is>
-      </c>
+      <c r="Q18" s="12" t="inlineStr"/>
       <c r="R18" s="12" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -1521,7 +1539,7 @@
       </c>
       <c r="S18" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -1529,24 +1547,24 @@
       <c r="A19" s="3" t="inlineStr"/>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>NU79Q12946</t>
+          <t>V74CH16111</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>12946</t>
+          <t>16111</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr"/>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>RL155 Peace Symbol Sterling Silver CZ Pendant</t>
+          <t>Enchanting Reindeer Crystal Bead Jewelry Mirror Box</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>All Products</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
@@ -1559,7 +1577,7 @@
         <v/>
       </c>
       <c r="L19" s="9" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M19" s="10">
         <f>IF(OR(L19="",K19="",L19=0),"",
@@ -1569,11 +1587,7 @@
       <c r="N19" s="11" t="inlineStr"/>
       <c r="O19" s="4" t="inlineStr"/>
       <c r="P19" s="4" t="inlineStr"/>
-      <c r="Q19" s="4" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/07/PhotoRoom-20230725_170302.png</t>
-        </is>
-      </c>
+      <c r="Q19" s="4" t="inlineStr"/>
       <c r="R19" s="4" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -1581,7 +1595,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -1589,24 +1603,24 @@
       <c r="A20" s="3" t="inlineStr"/>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>7BGS712948</t>
+          <t>5JS8X17078</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>12948</t>
+          <t>17078</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr"/>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>Z93 Teardrop Sterling Silver CZ Pendant</t>
+          <t>Floral Key Ring</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr"/>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>All Products</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H20" s="12" t="inlineStr"/>
@@ -1619,7 +1633,7 @@
         <v/>
       </c>
       <c r="L20" s="13" t="n">
-        <v>200</v>
+        <v>70</v>
       </c>
       <c r="M20" s="10">
         <f>IF(OR(L20="",K20="",L20=0),"",
@@ -1629,11 +1643,7 @@
       <c r="N20" s="11" t="inlineStr"/>
       <c r="O20" s="12" t="inlineStr"/>
       <c r="P20" s="12" t="inlineStr"/>
-      <c r="Q20" s="12" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/07/PhotoRoom-20230725_170237.png</t>
-        </is>
-      </c>
+      <c r="Q20" s="12" t="inlineStr"/>
       <c r="R20" s="12" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -1641,7 +1651,7 @@
       </c>
       <c r="S20" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -1649,24 +1659,24 @@
       <c r="A21" s="3" t="inlineStr"/>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>VJY7V12950</t>
+          <t>HU9YU17077</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>12950</t>
+          <t>17077</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr"/>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>SZ203 Multicolor CZ Stone Sterling Silver Bracelet</t>
+          <t>Heart Key Ring</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>All Products</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr"/>
@@ -1679,7 +1689,7 @@
         <v/>
       </c>
       <c r="L21" s="9" t="n">
-        <v>850</v>
+        <v>70</v>
       </c>
       <c r="M21" s="10">
         <f>IF(OR(L21="",K21="",L21=0),"",
@@ -1689,11 +1699,7 @@
       <c r="N21" s="11" t="inlineStr"/>
       <c r="O21" s="4" t="inlineStr"/>
       <c r="P21" s="4" t="inlineStr"/>
-      <c r="Q21" s="4" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/07/PhotoRoom-20230725_130330.webp</t>
-        </is>
-      </c>
+      <c r="Q21" s="4" t="inlineStr"/>
       <c r="R21" s="4" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -1701,7 +1707,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -1709,24 +1715,24 @@
       <c r="A22" s="3" t="inlineStr"/>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>5ENH612951</t>
+          <t>9ZWI213402</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>12951</t>
+          <t>13402</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr"/>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>Z71 Multicolor CZ Sterling Silver Ring</t>
+          <t>Jade Chain - Blue, Red &amp; Black</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr"/>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>All Products</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H22" s="12" t="inlineStr"/>
@@ -1738,9 +1744,7 @@
         <f>IF(I22="","",I22*(1+J22/100))</f>
         <v/>
       </c>
-      <c r="L22" s="13" t="n">
-        <v>550</v>
-      </c>
+      <c r="L22" s="6" t="inlineStr"/>
       <c r="M22" s="10">
         <f>IF(OR(L22="",K22="",L22=0),"",
   (L22-K22)/L22*100)</f>
@@ -1749,11 +1753,7 @@
       <c r="N22" s="11" t="inlineStr"/>
       <c r="O22" s="12" t="inlineStr"/>
       <c r="P22" s="12" t="inlineStr"/>
-      <c r="Q22" s="12" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/07/PhotoRoom-20230725_170040.png</t>
-        </is>
-      </c>
+      <c r="Q22" s="12" t="inlineStr"/>
       <c r="R22" s="12" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="S22" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -1769,24 +1769,24 @@
       <c r="A23" s="3" t="inlineStr"/>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>UOC3X12952</t>
+          <t>9ZWI213402-02</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>12952</t>
+          <t>13406</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr"/>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Z01 Black CZ Sterling Silver Tennis Bracelet</t>
+          <t>Jade Chain - Blue, Red &amp; Black - Small</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr"/>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>All Products</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
@@ -1799,7 +1799,7 @@
         <v/>
       </c>
       <c r="L23" s="9" t="n">
-        <v>450</v>
+        <v>350</v>
       </c>
       <c r="M23" s="10">
         <f>IF(OR(L23="",K23="",L23=0),"",
@@ -1809,11 +1809,7 @@
       <c r="N23" s="11" t="inlineStr"/>
       <c r="O23" s="4" t="inlineStr"/>
       <c r="P23" s="4" t="inlineStr"/>
-      <c r="Q23" s="4" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/07/PhotoRoom-20230725_165745.png</t>
-        </is>
-      </c>
+      <c r="Q23" s="4" t="inlineStr"/>
       <c r="R23" s="4" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -1821,7 +1817,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -1829,24 +1825,24 @@
       <c r="A24" s="3" t="inlineStr"/>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>UKQ6912953</t>
+          <t>9ZWI213402-01</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>12953</t>
+          <t>13405</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr"/>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>Z44 Sterling Silver Bracelet With Pink CZ</t>
+          <t>Jade Chain - Blue, Red &amp; Black - xl</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr"/>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>All Products</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H24" s="12" t="inlineStr"/>
@@ -1859,7 +1855,7 @@
         <v/>
       </c>
       <c r="L24" s="13" t="n">
-        <v>800</v>
+        <v>350</v>
       </c>
       <c r="M24" s="10">
         <f>IF(OR(L24="",K24="",L24=0),"",
@@ -1869,11 +1865,7 @@
       <c r="N24" s="11" t="inlineStr"/>
       <c r="O24" s="12" t="inlineStr"/>
       <c r="P24" s="12" t="inlineStr"/>
-      <c r="Q24" s="12" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/07/PhotoRoom-20230725_165854.png</t>
-        </is>
-      </c>
+      <c r="Q24" s="12" t="inlineStr"/>
       <c r="R24" s="12" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -1881,7 +1873,7 @@
       </c>
       <c r="S24" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -1889,24 +1881,24 @@
       <c r="A25" s="3" t="inlineStr"/>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>2D7BV12954</t>
+          <t>5452713411</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>12954</t>
+          <t>13411</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr"/>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Z506 Sterling Dome Silver Ring</t>
+          <t>Jade Chain - Corail, White &amp; Black with Gold Chain</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>All Products</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
@@ -1918,9 +1910,7 @@
         <f>IF(I25="","",I25*(1+J25/100))</f>
         <v/>
       </c>
-      <c r="L25" s="9" t="n">
-        <v>650</v>
-      </c>
+      <c r="L25" s="6" t="inlineStr"/>
       <c r="M25" s="10">
         <f>IF(OR(L25="",K25="",L25=0),"",
   (L25-K25)/L25*100)</f>
@@ -1929,11 +1919,7 @@
       <c r="N25" s="11" t="inlineStr"/>
       <c r="O25" s="4" t="inlineStr"/>
       <c r="P25" s="4" t="inlineStr"/>
-      <c r="Q25" s="4" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/07/PhotoRoom-20230725_170149.png</t>
-        </is>
-      </c>
+      <c r="Q25" s="4" t="inlineStr"/>
       <c r="R25" s="4" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -1941,7 +1927,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -1949,24 +1935,24 @@
       <c r="A26" s="3" t="inlineStr"/>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>969M212955</t>
+          <t>5452713411-01</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>12955</t>
+          <t>13416</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr"/>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>Z69 Multicolor CZ Hoop Sterling Silver Earrings</t>
+          <t>Jade Chain - Corail, White &amp; Black with Gold Chain - L</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr"/>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>All Products</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H26" s="12" t="inlineStr"/>
@@ -1979,7 +1965,7 @@
         <v/>
       </c>
       <c r="L26" s="13" t="n">
-        <v>1200</v>
+        <v>350</v>
       </c>
       <c r="M26" s="10">
         <f>IF(OR(L26="",K26="",L26=0),"",
@@ -1989,11 +1975,7 @@
       <c r="N26" s="11" t="inlineStr"/>
       <c r="O26" s="12" t="inlineStr"/>
       <c r="P26" s="12" t="inlineStr"/>
-      <c r="Q26" s="12" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/07/PhotoRoom-20230725_165548-1.png</t>
-        </is>
-      </c>
+      <c r="Q26" s="12" t="inlineStr"/>
       <c r="R26" s="12" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -2001,7 +1983,7 @@
       </c>
       <c r="S26" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -2009,24 +1991,24 @@
       <c r="A27" s="3" t="inlineStr"/>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>9CS3F12956</t>
+          <t>5452713411-02</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>12956</t>
+          <t>13417</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr"/>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>L107 Square Baguette Sterling Silver CZ Stud Earrings</t>
+          <t>Jade Chain - Corail, White &amp; Black with Gold Chain - Xl</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>All Products</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
@@ -2039,7 +2021,7 @@
         <v/>
       </c>
       <c r="L27" s="9" t="n">
-        <v>240</v>
+        <v>350</v>
       </c>
       <c r="M27" s="10">
         <f>IF(OR(L27="",K27="",L27=0),"",
@@ -2049,11 +2031,7 @@
       <c r="N27" s="11" t="inlineStr"/>
       <c r="O27" s="4" t="inlineStr"/>
       <c r="P27" s="4" t="inlineStr"/>
-      <c r="Q27" s="4" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/07/PhotoRoom-20230725_165230.png</t>
-        </is>
-      </c>
+      <c r="Q27" s="4" t="inlineStr"/>
       <c r="R27" s="4" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -2061,7 +2039,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -2069,24 +2047,24 @@
       <c r="A28" s="3" t="inlineStr"/>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>XE62E12957</t>
+          <t>9CS3F12956</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>12957</t>
+          <t>12956</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr"/>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>L167 Heartbeat Sterling Silver CZ Pendant</t>
+          <t>L107 Square Baguette Sterling Silver CZ Stud Earrings</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr"/>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>All Products</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H28" s="12" t="inlineStr"/>
@@ -2099,7 +2077,7 @@
         <v/>
       </c>
       <c r="L28" s="13" t="n">
-        <v>440</v>
+        <v>240</v>
       </c>
       <c r="M28" s="10">
         <f>IF(OR(L28="",K28="",L28=0),"",
@@ -2109,11 +2087,7 @@
       <c r="N28" s="11" t="inlineStr"/>
       <c r="O28" s="12" t="inlineStr"/>
       <c r="P28" s="12" t="inlineStr"/>
-      <c r="Q28" s="12" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/07/PhotoRoom-20230725_164419.png</t>
-        </is>
-      </c>
+      <c r="Q28" s="12" t="inlineStr"/>
       <c r="R28" s="12" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -2121,7 +2095,7 @@
       </c>
       <c r="S28" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -2129,24 +2103,24 @@
       <c r="A29" s="3" t="inlineStr"/>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>8WSK312958</t>
+          <t>QK39D12962</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>12958</t>
+          <t>12962</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr"/>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>N341 Sterling Silver Blue CZ Pendant And Chain</t>
+          <t>L138 Peacock Sterling Silver CZ Drop Earrings</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr"/>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>All Products</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
@@ -2159,7 +2133,7 @@
         <v/>
       </c>
       <c r="L29" s="9" t="n">
-        <v>220</v>
+        <v>750</v>
       </c>
       <c r="M29" s="10">
         <f>IF(OR(L29="",K29="",L29=0),"",
@@ -2169,11 +2143,7 @@
       <c r="N29" s="11" t="inlineStr"/>
       <c r="O29" s="4" t="inlineStr"/>
       <c r="P29" s="4" t="inlineStr"/>
-      <c r="Q29" s="4" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/07/PhotoRoom-20230725_165930.png</t>
-        </is>
-      </c>
+      <c r="Q29" s="4" t="inlineStr"/>
       <c r="R29" s="4" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -2181,7 +2151,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -2189,24 +2159,24 @@
       <c r="A30" s="3" t="inlineStr"/>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>U2PK712959</t>
+          <t>XE62E12957</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>12959</t>
+          <t>12957</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr"/>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>TL146 Round Sterling Silver CZ Chain</t>
+          <t>L167 Heartbeat Sterling Silver CZ Pendant</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr"/>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>All Products</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H30" s="12" t="inlineStr"/>
@@ -2219,7 +2189,7 @@
         <v/>
       </c>
       <c r="L30" s="13" t="n">
-        <v>650</v>
+        <v>440</v>
       </c>
       <c r="M30" s="10">
         <f>IF(OR(L30="",K30="",L30=0),"",
@@ -2229,11 +2199,7 @@
       <c r="N30" s="11" t="inlineStr"/>
       <c r="O30" s="12" t="inlineStr"/>
       <c r="P30" s="12" t="inlineStr"/>
-      <c r="Q30" s="12" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/07/PhotoRoom-20230725_194827.png</t>
-        </is>
-      </c>
+      <c r="Q30" s="12" t="inlineStr"/>
       <c r="R30" s="12" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -2241,7 +2207,7 @@
       </c>
       <c r="S30" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -2249,24 +2215,24 @@
       <c r="A31" s="3" t="inlineStr"/>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>66ARD12960</t>
+          <t>62IMR15723</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>12960</t>
+          <t>15723</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr"/>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>N12 Flower Trio Sterling Silver CZ Chain</t>
+          <t>L182 Core Heart Sterling Silver CZ Pendant</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>All Products</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
@@ -2279,7 +2245,7 @@
         <v/>
       </c>
       <c r="L31" s="9" t="n">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="M31" s="10">
         <f>IF(OR(L31="",K31="",L31=0),"",
@@ -2289,11 +2255,7 @@
       <c r="N31" s="11" t="inlineStr"/>
       <c r="O31" s="4" t="inlineStr"/>
       <c r="P31" s="4" t="inlineStr"/>
-      <c r="Q31" s="4" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/07/PhotoRoom-20230725_164639.png</t>
-        </is>
-      </c>
+      <c r="Q31" s="4" t="inlineStr"/>
       <c r="R31" s="4" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -2301,7 +2263,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -2309,24 +2271,24 @@
       <c r="A32" s="3" t="inlineStr"/>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>2BOFU12961</t>
+          <t>ELTW712254</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>12961</t>
+          <t>12254</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr"/>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>7N007 Dreamcatcher Sterling Silver CZ Pendant And Chain</t>
+          <t>Lightweight Jacket/Coat Sequin and Drawstring</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr"/>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>All Products</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H32" s="12" t="inlineStr"/>
@@ -2338,9 +2300,7 @@
         <f>IF(I32="","",I32*(1+J32/100))</f>
         <v/>
       </c>
-      <c r="L32" s="13" t="n">
-        <v>350</v>
-      </c>
+      <c r="L32" s="6" t="inlineStr"/>
       <c r="M32" s="10">
         <f>IF(OR(L32="",K32="",L32=0),"",
   (L32-K32)/L32*100)</f>
@@ -2349,11 +2309,7 @@
       <c r="N32" s="11" t="inlineStr"/>
       <c r="O32" s="12" t="inlineStr"/>
       <c r="P32" s="12" t="inlineStr"/>
-      <c r="Q32" s="12" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/07/7N007.png</t>
-        </is>
-      </c>
+      <c r="Q32" s="12" t="inlineStr"/>
       <c r="R32" s="12" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -2361,7 +2317,7 @@
       </c>
       <c r="S32" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -2369,24 +2325,24 @@
       <c r="A33" s="3" t="inlineStr"/>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>QK39D12962</t>
+          <t>ELTW712254-01</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>12962</t>
+          <t>14520</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr"/>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>L138 Peacock Sterling Silver CZ Drop Earrings</t>
+          <t>Lightweight Jacket/Coat Sequin and Drawstring - 32</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>All Products</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -2399,7 +2355,7 @@
         <v/>
       </c>
       <c r="L33" s="9" t="n">
-        <v>750</v>
+        <v>1850</v>
       </c>
       <c r="M33" s="10">
         <f>IF(OR(L33="",K33="",L33=0),"",
@@ -2409,11 +2365,7 @@
       <c r="N33" s="11" t="inlineStr"/>
       <c r="O33" s="4" t="inlineStr"/>
       <c r="P33" s="4" t="inlineStr"/>
-      <c r="Q33" s="4" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/07/PhotoRoom-20230725_165641.png</t>
-        </is>
-      </c>
+      <c r="Q33" s="4" t="inlineStr"/>
       <c r="R33" s="4" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -2421,7 +2373,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -2429,24 +2381,24 @@
       <c r="A34" s="3" t="inlineStr"/>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>894NH12964</t>
+          <t>ELTW712254-02</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>12964</t>
+          <t>14521</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr"/>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>Z746 Sterling Silver Purple CZ Studs</t>
+          <t>Lightweight Jacket/Coat Sequin and Drawstring - 34</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr"/>
       <c r="G34" s="12" t="inlineStr">
         <is>
-          <t>All Products</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H34" s="12" t="inlineStr"/>
@@ -2459,7 +2411,7 @@
         <v/>
       </c>
       <c r="L34" s="13" t="n">
-        <v>300</v>
+        <v>1850</v>
       </c>
       <c r="M34" s="10">
         <f>IF(OR(L34="",K34="",L34=0),"",
@@ -2469,11 +2421,7 @@
       <c r="N34" s="11" t="inlineStr"/>
       <c r="O34" s="12" t="inlineStr"/>
       <c r="P34" s="12" t="inlineStr"/>
-      <c r="Q34" s="12" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/07/PhotoRoom-20230725_194905.png</t>
-        </is>
-      </c>
+      <c r="Q34" s="12" t="inlineStr"/>
       <c r="R34" s="12" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -2481,7 +2429,7 @@
       </c>
       <c r="S34" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -2489,24 +2437,24 @@
       <c r="A35" s="3" t="inlineStr"/>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>P477412965</t>
+          <t>ELTW712254-03</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>12965</t>
+          <t>14522</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr"/>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Z247 Round Sterling Silver CZ Blue Stud Earrings</t>
+          <t>Lightweight Jacket/Coat Sequin and Drawstring - 36</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr"/>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>All Products</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr"/>
@@ -2519,7 +2467,7 @@
         <v/>
       </c>
       <c r="L35" s="9" t="n">
-        <v>300</v>
+        <v>1850</v>
       </c>
       <c r="M35" s="10">
         <f>IF(OR(L35="",K35="",L35=0),"",
@@ -2529,11 +2477,7 @@
       <c r="N35" s="11" t="inlineStr"/>
       <c r="O35" s="4" t="inlineStr"/>
       <c r="P35" s="4" t="inlineStr"/>
-      <c r="Q35" s="4" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/07/PhotoRoom-20230725_165110.png</t>
-        </is>
-      </c>
+      <c r="Q35" s="4" t="inlineStr"/>
       <c r="R35" s="4" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -2541,7 +2485,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -2549,24 +2493,24 @@
       <c r="A36" s="3" t="inlineStr"/>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>2ATS412971</t>
+          <t>ELTW712254-04</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>12971</t>
+          <t>14523</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr"/>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>N27 Leaf Sterling Silver CZ Bracelet</t>
+          <t>Lightweight Jacket/Coat Sequin and Drawstring - 38</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr"/>
       <c r="G36" s="12" t="inlineStr">
         <is>
-          <t>All Products</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H36" s="12" t="inlineStr"/>
@@ -2579,7 +2523,7 @@
         <v/>
       </c>
       <c r="L36" s="13" t="n">
-        <v>540</v>
+        <v>1850</v>
       </c>
       <c r="M36" s="10">
         <f>IF(OR(L36="",K36="",L36=0),"",
@@ -2589,11 +2533,7 @@
       <c r="N36" s="11" t="inlineStr"/>
       <c r="O36" s="12" t="inlineStr"/>
       <c r="P36" s="12" t="inlineStr"/>
-      <c r="Q36" s="12" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/07/PhotoRoom-20230725_194705.png</t>
-        </is>
-      </c>
+      <c r="Q36" s="12" t="inlineStr"/>
       <c r="R36" s="12" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -2601,7 +2541,7 @@
       </c>
       <c r="S36" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -2609,24 +2549,24 @@
       <c r="A37" s="3" t="inlineStr"/>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>8599F12977</t>
+          <t>628H913630</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>12977</t>
+          <t>13630</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr"/>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>SCH01 Sterling Silver Chain</t>
+          <t>Long Seige Dress with Stud Detail</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>All Products</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
@@ -2639,7 +2579,7 @@
         <v/>
       </c>
       <c r="L37" s="9" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="M37" s="10">
         <f>IF(OR(L37="",K37="",L37=0),"",
@@ -2649,11 +2589,7 @@
       <c r="N37" s="11" t="inlineStr"/>
       <c r="O37" s="4" t="inlineStr"/>
       <c r="P37" s="4" t="inlineStr"/>
-      <c r="Q37" s="4" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/07/PhotoRoom-20230725_165029.png</t>
-        </is>
-      </c>
+      <c r="Q37" s="4" t="inlineStr"/>
       <c r="R37" s="4" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -2661,7 +2597,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -2669,24 +2605,24 @@
       <c r="A38" s="3" t="inlineStr"/>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>6A1AU12978</t>
+          <t>7IB5W20260-1-1</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>12978</t>
+          <t>20270</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr"/>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>ER003 Sterling Silver Cluster CZ Hoop Earrings</t>
+          <t>Luxury Peel And Stick Flooring Tiles - F01804</t>
         </is>
       </c>
       <c r="F38" s="12" t="inlineStr"/>
       <c r="G38" s="12" t="inlineStr">
         <is>
-          <t>All Products</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H38" s="12" t="inlineStr"/>
@@ -2699,7 +2635,7 @@
         <v/>
       </c>
       <c r="L38" s="13" t="n">
-        <v>280</v>
+        <v>580</v>
       </c>
       <c r="M38" s="10">
         <f>IF(OR(L38="",K38="",L38=0),"",
@@ -2709,11 +2645,7 @@
       <c r="N38" s="11" t="inlineStr"/>
       <c r="O38" s="12" t="inlineStr"/>
       <c r="P38" s="12" t="inlineStr"/>
-      <c r="Q38" s="12" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/07/PhotoRoom-20230725_165310.png</t>
-        </is>
-      </c>
+      <c r="Q38" s="12" t="inlineStr"/>
       <c r="R38" s="12" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -2721,7 +2653,7 @@
       </c>
       <c r="S38" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -2729,24 +2661,24 @@
       <c r="A39" s="3" t="inlineStr"/>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>2O9IK12979</t>
+          <t>7IB5W20260-1-1-1</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>12979</t>
+          <t>20271</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr"/>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Men’s Sterling Silver And Black CZ Ring</t>
+          <t>Luxury Peel And Stick Flooring Tiles - F01805</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr"/>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>All Products</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
@@ -2759,7 +2691,7 @@
         <v/>
       </c>
       <c r="L39" s="9" t="n">
-        <v>850</v>
+        <v>580</v>
       </c>
       <c r="M39" s="10">
         <f>IF(OR(L39="",K39="",L39=0),"",
@@ -2769,11 +2701,7 @@
       <c r="N39" s="11" t="inlineStr"/>
       <c r="O39" s="4" t="inlineStr"/>
       <c r="P39" s="4" t="inlineStr"/>
-      <c r="Q39" s="4" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/07/PhotoRoom-20230725_170213.png</t>
-        </is>
-      </c>
+      <c r="Q39" s="4" t="inlineStr"/>
       <c r="R39" s="4" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -2781,7 +2709,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -2789,24 +2717,24 @@
       <c r="A40" s="3" t="inlineStr"/>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>LK8BE13198</t>
+          <t>7IB5W20260-1-1-1-1-1</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>13198</t>
+          <t>20273</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr"/>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>Z107 Sterling Silver CZ Ring</t>
+          <t>Luxury Peel And Stick Flooring Tiles - F01807</t>
         </is>
       </c>
       <c r="F40" s="12" t="inlineStr"/>
       <c r="G40" s="12" t="inlineStr">
         <is>
-          <t>All Products</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H40" s="12" t="inlineStr"/>
@@ -2819,7 +2747,7 @@
         <v/>
       </c>
       <c r="L40" s="13" t="n">
-        <v>390</v>
+        <v>580</v>
       </c>
       <c r="M40" s="10">
         <f>IF(OR(L40="",K40="",L40=0),"",
@@ -2829,11 +2757,7 @@
       <c r="N40" s="11" t="inlineStr"/>
       <c r="O40" s="12" t="inlineStr"/>
       <c r="P40" s="12" t="inlineStr"/>
-      <c r="Q40" s="12" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/07/PhotoRoom-20230725_165814.png</t>
-        </is>
-      </c>
+      <c r="Q40" s="12" t="inlineStr"/>
       <c r="R40" s="12" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -2841,7 +2765,7 @@
       </c>
       <c r="S40" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -2849,24 +2773,24 @@
       <c r="A41" s="3" t="inlineStr"/>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>9ZWI213402</t>
+          <t>7IB5W20260-1-1-1-1-1-1</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>13402</t>
+          <t>20274</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr"/>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Jade Chain - Blue, Red &amp; Black</t>
+          <t>Luxury Peel And Stick Flooring Tiles - F01808</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr"/>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>All Products</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
@@ -2878,7 +2802,9 @@
         <f>IF(I41="","",I41*(1+J41/100))</f>
         <v/>
       </c>
-      <c r="L41" s="6" t="inlineStr"/>
+      <c r="L41" s="9" t="n">
+        <v>580</v>
+      </c>
       <c r="M41" s="10">
         <f>IF(OR(L41="",K41="",L41=0),"",
   (L41-K41)/L41*100)</f>
@@ -2887,11 +2813,7 @@
       <c r="N41" s="11" t="inlineStr"/>
       <c r="O41" s="4" t="inlineStr"/>
       <c r="P41" s="4" t="inlineStr"/>
-      <c r="Q41" s="4" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/09/WhatsApp-Image-2023-09-01-at-07.24.02.jpeg, https://happyharvesting.co.za/wp-content/uploads/2023/09/WhatsApp-Image-2023-09-01-at-07.24.03.jpeg, https://happyharvesting.co.za/wp-content/uploads/2023/09/WhatsApp-Image-2023-09-01-at-07.24.04.jpeg, https://happyharvesting.co.za/wp-content/uploads/2023/09/WhatsApp-Image-2023-09-01-at-07.24.07.jpeg, https://happyharvesting.co.za/wp-content/uploads/2023/09/WhatsApp-Image-2023-09-01-at-07.24.07-1.jpeg</t>
-        </is>
-      </c>
+      <c r="Q41" s="4" t="inlineStr"/>
       <c r="R41" s="4" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -2899,7 +2821,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -2907,22 +2829,26 @@
       <c r="A42" s="3" t="inlineStr"/>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>9ZWI213402-01</t>
+          <t>7IB5W20260-1-1-1-1-1-1-1</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>13405</t>
+          <t>20275</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr"/>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>Jade Chain - Blue, Red &amp; Black - xl</t>
+          <t>Luxury Peel And Stick Flooring Tiles - F01809</t>
         </is>
       </c>
       <c r="F42" s="12" t="inlineStr"/>
-      <c r="G42" s="12" t="inlineStr"/>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
       <c r="H42" s="12" t="inlineStr"/>
       <c r="I42" s="6" t="inlineStr"/>
       <c r="J42" s="7" t="n">
@@ -2933,7 +2859,7 @@
         <v/>
       </c>
       <c r="L42" s="13" t="n">
-        <v>350</v>
+        <v>580</v>
       </c>
       <c r="M42" s="10">
         <f>IF(OR(L42="",K42="",L42=0),"",
@@ -2951,7 +2877,7 @@
       </c>
       <c r="S42" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -2959,22 +2885,26 @@
       <c r="A43" s="3" t="inlineStr"/>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>9ZWI213402-02</t>
+          <t>7IB5W20260-1</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>13406</t>
+          <t>20269</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr"/>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Jade Chain - Blue, Red &amp; Black - Small</t>
+          <t>Luxury Peel And Stick Flooring Tiles - F01810</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr"/>
-      <c r="G43" s="4" t="inlineStr"/>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
       <c r="H43" s="4" t="inlineStr"/>
       <c r="I43" s="6" t="inlineStr"/>
       <c r="J43" s="7" t="n">
@@ -2985,7 +2915,7 @@
         <v/>
       </c>
       <c r="L43" s="9" t="n">
-        <v>350</v>
+        <v>580</v>
       </c>
       <c r="M43" s="10">
         <f>IF(OR(L43="",K43="",L43=0),"",
@@ -3003,7 +2933,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -3011,24 +2941,24 @@
       <c r="A44" s="3" t="inlineStr"/>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>5452713411</t>
+          <t>7IB5W20260-1-1-1-1</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>13411</t>
+          <t>20272</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr"/>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>Jade Chain - Corail, White &amp; Black with Gold Chain</t>
+          <t>Luxury Peel And Stick Flooring Tiles - F01812</t>
         </is>
       </c>
       <c r="F44" s="12" t="inlineStr"/>
       <c r="G44" s="12" t="inlineStr">
         <is>
-          <t>All Products</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H44" s="12" t="inlineStr"/>
@@ -3040,7 +2970,9 @@
         <f>IF(I44="","",I44*(1+J44/100))</f>
         <v/>
       </c>
-      <c r="L44" s="6" t="inlineStr"/>
+      <c r="L44" s="13" t="n">
+        <v>580</v>
+      </c>
       <c r="M44" s="10">
         <f>IF(OR(L44="",K44="",L44=0),"",
   (L44-K44)/L44*100)</f>
@@ -3049,11 +2981,7 @@
       <c r="N44" s="11" t="inlineStr"/>
       <c r="O44" s="12" t="inlineStr"/>
       <c r="P44" s="12" t="inlineStr"/>
-      <c r="Q44" s="12" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/09/WhatsApp-Image-2023-09-01-at-07.24.09.jpeg, https://happyharvesting.co.za/wp-content/uploads/2023/09/WhatsApp-Image-2023-09-01-at-07.24.08.jpeg, https://happyharvesting.co.za/wp-content/uploads/2023/09/WhatsApp-Image-2023-09-01-at-07.24.10-1.jpeg, https://happyharvesting.co.za/wp-content/uploads/2023/09/WhatsApp-Image-2023-09-01-at-07.24.10-2.jpeg</t>
-        </is>
-      </c>
+      <c r="Q44" s="12" t="inlineStr"/>
       <c r="R44" s="12" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -3061,7 +2989,7 @@
       </c>
       <c r="S44" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -3069,22 +2997,26 @@
       <c r="A45" s="3" t="inlineStr"/>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>5452713411-01</t>
+          <t>7IB5W20260</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>13416</t>
+          <t>20260</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr"/>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Jade Chain - Corail, White &amp; Black with Gold Chain - L</t>
+          <t>Luxury Peel And Stick Flooring Tiles - F01813</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr"/>
-      <c r="G45" s="4" t="inlineStr"/>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
       <c r="H45" s="4" t="inlineStr"/>
       <c r="I45" s="6" t="inlineStr"/>
       <c r="J45" s="7" t="n">
@@ -3095,7 +3027,7 @@
         <v/>
       </c>
       <c r="L45" s="9" t="n">
-        <v>350</v>
+        <v>580</v>
       </c>
       <c r="M45" s="10">
         <f>IF(OR(L45="",K45="",L45=0),"",
@@ -3113,7 +3045,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -3121,22 +3053,26 @@
       <c r="A46" s="3" t="inlineStr"/>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>5452713411-02</t>
+          <t>ME-650-VU</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>13417</t>
+          <t>11830</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr"/>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>Jade Chain - Corail, White &amp; Black with Gold Chain - Xl</t>
+          <t>Mecer UPS with AVR,Monitoring Software + Cable &amp; Built-in Surge Protection</t>
         </is>
       </c>
       <c r="F46" s="12" t="inlineStr"/>
-      <c r="G46" s="12" t="inlineStr"/>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
       <c r="H46" s="12" t="inlineStr"/>
       <c r="I46" s="6" t="inlineStr"/>
       <c r="J46" s="7" t="n">
@@ -3146,9 +3082,7 @@
         <f>IF(I46="","",I46*(1+J46/100))</f>
         <v/>
       </c>
-      <c r="L46" s="13" t="n">
-        <v>350</v>
-      </c>
+      <c r="L46" s="6" t="inlineStr"/>
       <c r="M46" s="10">
         <f>IF(OR(L46="",K46="",L46=0),"",
   (L46-K46)/L46*100)</f>
@@ -3165,7 +3099,7 @@
       </c>
       <c r="S46" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -3173,22 +3107,26 @@
       <c r="A47" s="3" t="inlineStr"/>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>ELTW712254-01</t>
+          <t>ME-650-VU-02</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>14520</t>
+          <t>11839</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr"/>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Lightweight Jacket/Coat Sequin and Drawstring - 32</t>
+          <t>Mecer UPS with AVR,Monitoring Software + Cable &amp; Built-in Surge Protection - ME-1000-VU Mecer 1000VA / 600W OFF-LINE UPS</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr"/>
-      <c r="G47" s="4" t="inlineStr"/>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
       <c r="H47" s="4" t="inlineStr"/>
       <c r="I47" s="6" t="inlineStr"/>
       <c r="J47" s="7" t="n">
@@ -3199,7 +3137,7 @@
         <v/>
       </c>
       <c r="L47" s="9" t="n">
-        <v>1850</v>
+        <v>2100</v>
       </c>
       <c r="M47" s="10">
         <f>IF(OR(L47="",K47="",L47=0),"",
@@ -3217,7 +3155,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -3225,22 +3163,26 @@
       <c r="A48" s="3" t="inlineStr"/>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>ELTW712254-02</t>
+          <t>ME-650-VU-05</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>14521</t>
+          <t>11842</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr"/>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>Lightweight Jacket/Coat Sequin and Drawstring - 34</t>
+          <t>Mecer UPS with AVR,Monitoring Software + Cable &amp; Built-in Surge Protection - ME-1000-WPTU+ Mecer 1000VA / 800W ON-LINE UPS</t>
         </is>
       </c>
       <c r="F48" s="12" t="inlineStr"/>
-      <c r="G48" s="12" t="inlineStr"/>
+      <c r="G48" s="12" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
       <c r="H48" s="12" t="inlineStr"/>
       <c r="I48" s="6" t="inlineStr"/>
       <c r="J48" s="7" t="n">
@@ -3251,7 +3193,7 @@
         <v/>
       </c>
       <c r="L48" s="13" t="n">
-        <v>1850</v>
+        <v>4550</v>
       </c>
       <c r="M48" s="10">
         <f>IF(OR(L48="",K48="",L48=0),"",
@@ -3269,7 +3211,7 @@
       </c>
       <c r="S48" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -3277,22 +3219,26 @@
       <c r="A49" s="3" t="inlineStr"/>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>ELTW712254-03</t>
+          <t>ME-650-VU-09</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>14522</t>
+          <t>11846</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr"/>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Lightweight Jacket/Coat Sequin and Drawstring - 36</t>
+          <t>Mecer UPS with AVR,Monitoring Software + Cable &amp; Built-in Surge Protection - ME-10000-WPTV Mecer 10000VA / 10000W ON-LINE UPS</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr"/>
-      <c r="G49" s="4" t="inlineStr"/>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
       <c r="H49" s="4" t="inlineStr"/>
       <c r="I49" s="6" t="inlineStr"/>
       <c r="J49" s="7" t="n">
@@ -3303,7 +3249,7 @@
         <v/>
       </c>
       <c r="L49" s="9" t="n">
-        <v>1850</v>
+        <v>22500</v>
       </c>
       <c r="M49" s="10">
         <f>IF(OR(L49="",K49="",L49=0),"",
@@ -3321,7 +3267,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -3329,22 +3275,26 @@
       <c r="A50" s="3" t="inlineStr"/>
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>ELTW712254-04</t>
+          <t>ME-650-VU-03</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>14523</t>
+          <t>11840</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr"/>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>Lightweight Jacket/Coat Sequin and Drawstring - 38</t>
+          <t>Mecer UPS with AVR,Monitoring Software + Cable &amp; Built-in Surge Protection - ME-2000-VU Mecer 2000VA / 1200W OFF-LINE UPS</t>
         </is>
       </c>
       <c r="F50" s="12" t="inlineStr"/>
-      <c r="G50" s="12" t="inlineStr"/>
+      <c r="G50" s="12" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
       <c r="H50" s="12" t="inlineStr"/>
       <c r="I50" s="6" t="inlineStr"/>
       <c r="J50" s="7" t="n">
@@ -3355,7 +3305,7 @@
         <v/>
       </c>
       <c r="L50" s="13" t="n">
-        <v>1850</v>
+        <v>3000</v>
       </c>
       <c r="M50" s="10">
         <f>IF(OR(L50="",K50="",L50=0),"",
@@ -3373,7 +3323,7 @@
       </c>
       <c r="S50" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -3381,24 +3331,24 @@
       <c r="A51" s="3" t="inlineStr"/>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>RINGL</t>
+          <t>ME-650-VU-06</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>15340</t>
+          <t>11843</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr"/>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>RGB LED Soft Ring Light</t>
+          <t>Mecer UPS with AVR,Monitoring Software + Cable &amp; Built-in Surge Protection - ME-2000-WPTU+ Mecer 2000VA / 1600W ON-LINE UPS</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr"/>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>Hardware &gt; Electrical</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
@@ -3411,7 +3361,7 @@
         <v/>
       </c>
       <c r="L51" s="9" t="n">
-        <v>500</v>
+        <v>7350</v>
       </c>
       <c r="M51" s="10">
         <f>IF(OR(L51="",K51="",L51=0),"",
@@ -3421,11 +3371,7 @@
       <c r="N51" s="11" t="inlineStr"/>
       <c r="O51" s="4" t="inlineStr"/>
       <c r="P51" s="4" t="inlineStr"/>
-      <c r="Q51" s="4" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/12/soft-lyt.webp, https://happyharvesting.co.za/wp-content/uploads/2023/12/WhatsApp-Image-2023-12-06-at-4.15.17-PM.jpeg</t>
-        </is>
-      </c>
+      <c r="Q51" s="4" t="inlineStr"/>
       <c r="R51" s="4" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -3433,7 +3379,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -3441,24 +3387,24 @@
       <c r="A52" s="3" t="inlineStr"/>
       <c r="B52" s="12" t="inlineStr">
         <is>
-          <t>LSL</t>
+          <t>ME-650-VU-04</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>15503</t>
+          <t>11841</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr"/>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>50m LED String Lights - TYN-060- all colors</t>
+          <t>Mecer UPS with AVR,Monitoring Software + Cable &amp; Built-in Surge Protection - ME-3000-VU+ Mecer 3000VA / 1800W OFF-LINE UPS</t>
         </is>
       </c>
       <c r="F52" s="12" t="inlineStr"/>
       <c r="G52" s="12" t="inlineStr">
         <is>
-          <t>Homeware &gt; Decor</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H52" s="12" t="inlineStr"/>
@@ -3471,7 +3417,7 @@
         <v/>
       </c>
       <c r="L52" s="13" t="n">
-        <v>250</v>
+        <v>5450</v>
       </c>
       <c r="M52" s="10">
         <f>IF(OR(L52="",K52="",L52=0),"",
@@ -3481,11 +3427,7 @@
       <c r="N52" s="11" t="inlineStr"/>
       <c r="O52" s="12" t="inlineStr"/>
       <c r="P52" s="12" t="inlineStr"/>
-      <c r="Q52" s="12" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/12/Photo-2023-12-08-22-09-45.jpg</t>
-        </is>
-      </c>
+      <c r="Q52" s="12" t="inlineStr"/>
       <c r="R52" s="12" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -3493,7 +3435,7 @@
       </c>
       <c r="S52" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -3501,24 +3443,24 @@
       <c r="A53" s="3" t="inlineStr"/>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>996A115690</t>
+          <t>ME-650-VU-07</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>15690</t>
+          <t>11844</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>X07 CZ Baguette Tennis Bracelet</t>
+          <t>Mecer UPS with AVR,Monitoring Software + Cable &amp; Built-in Surge Protection - ME-3000-WPTV Mecer 3000VA / 2700W ON-LINE UPS</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr"/>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>Lifestyle &amp; Everyday Essentials &gt; Jewellery</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
@@ -3531,7 +3473,7 @@
         <v/>
       </c>
       <c r="L53" s="9" t="n">
-        <v>1100</v>
+        <v>10650</v>
       </c>
       <c r="M53" s="10">
         <f>IF(OR(L53="",K53="",L53=0),"",
@@ -3541,11 +3483,7 @@
       <c r="N53" s="11" t="inlineStr"/>
       <c r="O53" s="4" t="inlineStr"/>
       <c r="P53" s="4" t="inlineStr"/>
-      <c r="Q53" s="4" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/12/PhotoRoom-20231218_104105.png</t>
-        </is>
-      </c>
+      <c r="Q53" s="4" t="inlineStr"/>
       <c r="R53" s="4" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -3553,7 +3491,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -3561,24 +3499,24 @@
       <c r="A54" s="3" t="inlineStr"/>
       <c r="B54" s="12" t="inlineStr">
         <is>
-          <t>747RC15691</t>
+          <t>ME-650-VU-08</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>15691</t>
+          <t>11845</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr"/>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>X28 CZ Tennis Bracelet</t>
+          <t>Mecer UPS with AVR,Monitoring Software + Cable &amp; Built-in Surge Protection - ME-6000-WPTV Mecer 6000VA / 6000W ON-LINE UPS</t>
         </is>
       </c>
       <c r="F54" s="12" t="inlineStr"/>
       <c r="G54" s="12" t="inlineStr">
         <is>
-          <t>Lifestyle &amp; Everyday Essentials &gt; Jewellery</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H54" s="12" t="inlineStr"/>
@@ -3591,7 +3529,7 @@
         <v/>
       </c>
       <c r="L54" s="13" t="n">
-        <v>1200</v>
+        <v>19900</v>
       </c>
       <c r="M54" s="10">
         <f>IF(OR(L54="",K54="",L54=0),"",
@@ -3601,11 +3539,7 @@
       <c r="N54" s="11" t="inlineStr"/>
       <c r="O54" s="12" t="inlineStr"/>
       <c r="P54" s="12" t="inlineStr"/>
-      <c r="Q54" s="12" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/12/PhotoRoom-20231218_110134-1.png</t>
-        </is>
-      </c>
+      <c r="Q54" s="12" t="inlineStr"/>
       <c r="R54" s="12" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -3613,7 +3547,7 @@
       </c>
       <c r="S54" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -3621,24 +3555,24 @@
       <c r="A55" s="3" t="inlineStr"/>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>UM73O15692</t>
+          <t>ME-650-VU-10</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>15692</t>
+          <t>11975</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr"/>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>X23 Round CZ Tennis Bracelet</t>
+          <t>Mecer UPS with AVR,Monitoring Software + Cable &amp; Built-in Surge Protection - ME-650-VU 650VA OFF-LINE UPS</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr"/>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>Lifestyle &amp; Everyday Essentials &gt; Jewellery</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
@@ -3651,7 +3585,7 @@
         <v/>
       </c>
       <c r="L55" s="9" t="n">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="M55" s="10">
         <f>IF(OR(L55="",K55="",L55=0),"",
@@ -3661,11 +3595,7 @@
       <c r="N55" s="11" t="inlineStr"/>
       <c r="O55" s="4" t="inlineStr"/>
       <c r="P55" s="4" t="inlineStr"/>
-      <c r="Q55" s="4" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/12/PhotoRoom-20231218_105841.png</t>
-        </is>
-      </c>
+      <c r="Q55" s="4" t="inlineStr"/>
       <c r="R55" s="4" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -3673,7 +3603,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -3681,24 +3611,24 @@
       <c r="A56" s="3" t="inlineStr"/>
       <c r="B56" s="12" t="inlineStr">
         <is>
-          <t>ALY9V15693</t>
+          <t>ME-650-VU-01</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>15693</t>
+          <t>11838</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr"/>
       <c r="E56" s="12" t="inlineStr">
         <is>
-          <t>X09 Snake CZ Tennis Bracelet</t>
+          <t>Mecer UPS with AVR,Monitoring Software + Cable &amp; Built-in Surge Protection - ME-850-VU Mecer 850VA / 480W OFF-LINE UPS</t>
         </is>
       </c>
       <c r="F56" s="12" t="inlineStr"/>
       <c r="G56" s="12" t="inlineStr">
         <is>
-          <t>Lifestyle &amp; Everyday Essentials &gt; Jewellery</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H56" s="12" t="inlineStr"/>
@@ -3711,7 +3641,7 @@
         <v/>
       </c>
       <c r="L56" s="13" t="n">
-        <v>950</v>
+        <v>1900</v>
       </c>
       <c r="M56" s="10">
         <f>IF(OR(L56="",K56="",L56=0),"",
@@ -3721,11 +3651,7 @@
       <c r="N56" s="11" t="inlineStr"/>
       <c r="O56" s="12" t="inlineStr"/>
       <c r="P56" s="12" t="inlineStr"/>
-      <c r="Q56" s="12" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/12/PhotoRoom-20231218_105415.png</t>
-        </is>
-      </c>
+      <c r="Q56" s="12" t="inlineStr"/>
       <c r="R56" s="12" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -3733,7 +3659,7 @@
       </c>
       <c r="S56" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -3741,24 +3667,24 @@
       <c r="A57" s="3" t="inlineStr"/>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>LUZ5U15694</t>
+          <t>2O9IK12979</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>15694</t>
+          <t>12979</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr"/>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>X16 Round Delicate CZ Tennis Bracelet</t>
+          <t>Men’s Sterling Silver And Black CZ Ring</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr"/>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>Lifestyle &amp; Everyday Essentials &gt; Jewellery</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
@@ -3771,7 +3697,7 @@
         <v/>
       </c>
       <c r="L57" s="9" t="n">
-        <v>800</v>
+        <v>850</v>
       </c>
       <c r="M57" s="10">
         <f>IF(OR(L57="",K57="",L57=0),"",
@@ -3781,11 +3707,7 @@
       <c r="N57" s="11" t="inlineStr"/>
       <c r="O57" s="4" t="inlineStr"/>
       <c r="P57" s="4" t="inlineStr"/>
-      <c r="Q57" s="4" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/12/1000016271.png</t>
-        </is>
-      </c>
+      <c r="Q57" s="4" t="inlineStr"/>
       <c r="R57" s="4" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -3793,7 +3715,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -3801,24 +3723,24 @@
       <c r="A58" s="3" t="inlineStr"/>
       <c r="B58" s="12" t="inlineStr">
         <is>
-          <t>GKB3515695</t>
+          <t>F02243</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>15695</t>
+          <t>9808</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr"/>
       <c r="E58" s="12" t="inlineStr">
         <is>
-          <t>X19 Teardrop CZ Tennis Bracelet</t>
+          <t>Mobile &amp; Jewellery Precision 5 Piece Screwdriver Set</t>
         </is>
       </c>
       <c r="F58" s="12" t="inlineStr"/>
       <c r="G58" s="12" t="inlineStr">
         <is>
-          <t>Lifestyle &amp; Everyday Essentials &gt; Jewellery</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H58" s="12" t="inlineStr"/>
@@ -3831,7 +3753,7 @@
         <v/>
       </c>
       <c r="L58" s="13" t="n">
-        <v>1200</v>
+        <v>200</v>
       </c>
       <c r="M58" s="10">
         <f>IF(OR(L58="",K58="",L58=0),"",
@@ -3841,11 +3763,7 @@
       <c r="N58" s="11" t="inlineStr"/>
       <c r="O58" s="12" t="inlineStr"/>
       <c r="P58" s="12" t="inlineStr"/>
-      <c r="Q58" s="12" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/12/PhotoRoom-20231213_212031.png</t>
-        </is>
-      </c>
+      <c r="Q58" s="12" t="inlineStr"/>
       <c r="R58" s="12" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -3853,7 +3771,7 @@
       </c>
       <c r="S58" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -3861,24 +3779,24 @@
       <c r="A59" s="3" t="inlineStr"/>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>LC39F15711</t>
+          <t>66ARD12960</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>15711</t>
+          <t>12960</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr"/>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>X21 Slabbed CZ Tennis Bracelet</t>
+          <t>N12 Flower Trio Sterling Silver CZ Chain</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr"/>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>Lifestyle &amp; Everyday Essentials &gt; Jewellery</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
@@ -3891,7 +3809,7 @@
         <v/>
       </c>
       <c r="L59" s="9" t="n">
-        <v>1500</v>
+        <v>800</v>
       </c>
       <c r="M59" s="10">
         <f>IF(OR(L59="",K59="",L59=0),"",
@@ -3901,11 +3819,7 @@
       <c r="N59" s="11" t="inlineStr"/>
       <c r="O59" s="4" t="inlineStr"/>
       <c r="P59" s="4" t="inlineStr"/>
-      <c r="Q59" s="4" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/12/PhotoRoom-20231218_104511.png</t>
-        </is>
-      </c>
+      <c r="Q59" s="4" t="inlineStr"/>
       <c r="R59" s="4" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -3913,7 +3827,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -3921,24 +3835,24 @@
       <c r="A60" s="3" t="inlineStr"/>
       <c r="B60" s="12" t="inlineStr">
         <is>
-          <t>T8D7Y15712</t>
+          <t>2ATS412971</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>15712</t>
+          <t>12971</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr"/>
       <c r="E60" s="12" t="inlineStr">
         <is>
-          <t>X15 Morse CZ Tennis Bracelet</t>
+          <t>N27 Leaf Sterling Silver CZ Bracelet</t>
         </is>
       </c>
       <c r="F60" s="12" t="inlineStr"/>
       <c r="G60" s="12" t="inlineStr">
         <is>
-          <t>Lifestyle &amp; Everyday Essentials &gt; Jewellery</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H60" s="12" t="inlineStr"/>
@@ -3951,7 +3865,7 @@
         <v/>
       </c>
       <c r="L60" s="13" t="n">
-        <v>950</v>
+        <v>540</v>
       </c>
       <c r="M60" s="10">
         <f>IF(OR(L60="",K60="",L60=0),"",
@@ -3961,11 +3875,7 @@
       <c r="N60" s="11" t="inlineStr"/>
       <c r="O60" s="12" t="inlineStr"/>
       <c r="P60" s="12" t="inlineStr"/>
-      <c r="Q60" s="12" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/12/PhotoRoom-20231213_213528.png</t>
-        </is>
-      </c>
+      <c r="Q60" s="12" t="inlineStr"/>
       <c r="R60" s="12" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -3973,7 +3883,7 @@
       </c>
       <c r="S60" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -3981,24 +3891,24 @@
       <c r="A61" s="3" t="inlineStr"/>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>3I91N15714</t>
+          <t>8WSK312958</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>15714</t>
+          <t>12958</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr"/>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>X03 CZ Square Stone Tennis Necklace</t>
+          <t>N341 Sterling Silver Blue CZ Pendant And Chain</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr"/>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>Lifestyle &amp; Everyday Essentials &gt; Jewellery</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
@@ -4011,7 +3921,7 @@
         <v/>
       </c>
       <c r="L61" s="9" t="n">
-        <v>2950</v>
+        <v>220</v>
       </c>
       <c r="M61" s="10">
         <f>IF(OR(L61="",K61="",L61=0),"",
@@ -4021,11 +3931,7 @@
       <c r="N61" s="11" t="inlineStr"/>
       <c r="O61" s="4" t="inlineStr"/>
       <c r="P61" s="4" t="inlineStr"/>
-      <c r="Q61" s="4" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/12/PhotoRoom-20231218_111120.png</t>
-        </is>
-      </c>
+      <c r="Q61" s="4" t="inlineStr"/>
       <c r="R61" s="4" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -4033,7 +3939,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -4041,24 +3947,24 @@
       <c r="A62" s="3" t="inlineStr"/>
       <c r="B62" s="12" t="inlineStr">
         <is>
-          <t>3YW8S15715</t>
+          <t>J35FR13569</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>15715</t>
+          <t>13569</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr"/>
       <c r="E62" s="12" t="inlineStr">
         <is>
-          <t>Z92 Round Sterling Silver CZ Pendant</t>
+          <t>Navy Stud Chiffon Dress</t>
         </is>
       </c>
       <c r="F62" s="12" t="inlineStr"/>
       <c r="G62" s="12" t="inlineStr">
         <is>
-          <t>All Products</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H62" s="12" t="inlineStr"/>
@@ -4071,7 +3977,7 @@
         <v/>
       </c>
       <c r="L62" s="13" t="n">
-        <v>150</v>
+        <v>800</v>
       </c>
       <c r="M62" s="10">
         <f>IF(OR(L62="",K62="",L62=0),"",
@@ -4081,11 +3987,7 @@
       <c r="N62" s="11" t="inlineStr"/>
       <c r="O62" s="12" t="inlineStr"/>
       <c r="P62" s="12" t="inlineStr"/>
-      <c r="Q62" s="12" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/12/PhotoRoom-20231218_100504.png</t>
-        </is>
-      </c>
+      <c r="Q62" s="12" t="inlineStr"/>
       <c r="R62" s="12" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -4093,7 +3995,7 @@
       </c>
       <c r="S62" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -4101,24 +4003,24 @@
       <c r="A63" s="3" t="inlineStr"/>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>OW22115716</t>
+          <t>HXRCG15726</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>15716</t>
+          <t>15726</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr"/>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>Z61 Tree Sterling Silver CZ Pendant</t>
+          <t>R701 Infinity Sterling Silver CZ Earrings &amp; Pendant</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr"/>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>All Products</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr"/>
@@ -4131,7 +4033,7 @@
         <v/>
       </c>
       <c r="L63" s="9" t="n">
-        <v>300</v>
+        <v>430</v>
       </c>
       <c r="M63" s="10">
         <f>IF(OR(L63="",K63="",L63=0),"",
@@ -4141,11 +4043,7 @@
       <c r="N63" s="11" t="inlineStr"/>
       <c r="O63" s="4" t="inlineStr"/>
       <c r="P63" s="4" t="inlineStr"/>
-      <c r="Q63" s="4" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/12/PhotoRoom-20231218_095243-1.png</t>
-        </is>
-      </c>
+      <c r="Q63" s="4" t="inlineStr"/>
       <c r="R63" s="4" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -4153,7 +4051,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -4161,24 +4059,24 @@
       <c r="A64" s="3" t="inlineStr"/>
       <c r="B64" s="12" t="inlineStr">
         <is>
-          <t>Y9MNO15717</t>
+          <t>KJR2P15720</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>15717</t>
+          <t>15720</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr"/>
       <c r="E64" s="12" t="inlineStr">
         <is>
-          <t>R79 Crown Heart Sterling Silver CZ Pendant</t>
+          <t>R76 Arch Heart Sterling Silver CZ Pendant</t>
         </is>
       </c>
       <c r="F64" s="12" t="inlineStr"/>
       <c r="G64" s="12" t="inlineStr">
         <is>
-          <t>All Products</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H64" s="12" t="inlineStr"/>
@@ -4191,7 +4089,7 @@
         <v/>
       </c>
       <c r="L64" s="13" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="M64" s="10">
         <f>IF(OR(L64="",K64="",L64=0),"",
@@ -4201,11 +4099,7 @@
       <c r="N64" s="11" t="inlineStr"/>
       <c r="O64" s="12" t="inlineStr"/>
       <c r="P64" s="12" t="inlineStr"/>
-      <c r="Q64" s="12" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/12/PhotoRoom-20231218_092430.png</t>
-        </is>
-      </c>
+      <c r="Q64" s="12" t="inlineStr"/>
       <c r="R64" s="12" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -4213,7 +4107,7 @@
       </c>
       <c r="S64" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -4221,24 +4115,24 @@
       <c r="A65" s="3" t="inlineStr"/>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>JD25O15718</t>
+          <t>8S8D215724</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>15718</t>
+          <t>15724</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr"/>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>Z91 Double Heart Sterling Silver CZ Pendant</t>
+          <t>R78 Clock Sterling Silver CZ Pendant</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr"/>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>All Products</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
@@ -4251,7 +4145,7 @@
         <v/>
       </c>
       <c r="L65" s="9" t="n">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="M65" s="10">
         <f>IF(OR(L65="",K65="",L65=0),"",
@@ -4261,11 +4155,7 @@
       <c r="N65" s="11" t="inlineStr"/>
       <c r="O65" s="4" t="inlineStr"/>
       <c r="P65" s="4" t="inlineStr"/>
-      <c r="Q65" s="4" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/12/PhotoRoom-20231213_214116.png</t>
-        </is>
-      </c>
+      <c r="Q65" s="4" t="inlineStr"/>
       <c r="R65" s="4" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -4273,7 +4163,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -4281,24 +4171,24 @@
       <c r="A66" s="3" t="inlineStr"/>
       <c r="B66" s="12" t="inlineStr">
         <is>
-          <t>KJR2P15720</t>
+          <t>Y9MNO15717</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>15720</t>
+          <t>15717</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr"/>
       <c r="E66" s="12" t="inlineStr">
         <is>
-          <t>R76 Arch Heart Sterling Silver CZ Pendant</t>
+          <t>R79 Crown Heart Sterling Silver CZ Pendant</t>
         </is>
       </c>
       <c r="F66" s="12" t="inlineStr"/>
       <c r="G66" s="12" t="inlineStr">
         <is>
-          <t>All Products</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H66" s="12" t="inlineStr"/>
@@ -4311,7 +4201,7 @@
         <v/>
       </c>
       <c r="L66" s="13" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="M66" s="10">
         <f>IF(OR(L66="",K66="",L66=0),"",
@@ -4321,11 +4211,7 @@
       <c r="N66" s="11" t="inlineStr"/>
       <c r="O66" s="12" t="inlineStr"/>
       <c r="P66" s="12" t="inlineStr"/>
-      <c r="Q66" s="12" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/12/PhotoRoom-20231218_092946.png</t>
-        </is>
-      </c>
+      <c r="Q66" s="12" t="inlineStr"/>
       <c r="R66" s="12" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -4333,7 +4219,7 @@
       </c>
       <c r="S66" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -4341,24 +4227,24 @@
       <c r="A67" s="3" t="inlineStr"/>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>2W4VQ15722</t>
+          <t>RINGL</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>15722</t>
+          <t>15340</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr"/>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>Z116 Twin Tails Heart Sterling Silver CZ Pendant</t>
+          <t>RGB LED Soft Ring Light</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr"/>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>Lifestyle &amp; Everyday Essentials &gt; Jewellery</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
@@ -4371,7 +4257,7 @@
         <v/>
       </c>
       <c r="L67" s="9" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="M67" s="10">
         <f>IF(OR(L67="",K67="",L67=0),"",
@@ -4381,11 +4267,7 @@
       <c r="N67" s="11" t="inlineStr"/>
       <c r="O67" s="4" t="inlineStr"/>
       <c r="P67" s="4" t="inlineStr"/>
-      <c r="Q67" s="4" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/12/PhotoRoom-20231218_093949.png</t>
-        </is>
-      </c>
+      <c r="Q67" s="4" t="inlineStr"/>
       <c r="R67" s="4" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -4393,7 +4275,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -4401,24 +4283,24 @@
       <c r="A68" s="3" t="inlineStr"/>
       <c r="B68" s="12" t="inlineStr">
         <is>
-          <t>62IMR15723</t>
+          <t>NU79Q12946</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>15723</t>
+          <t>12946</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr"/>
       <c r="E68" s="12" t="inlineStr">
         <is>
-          <t>L182 Core Heart Sterling Silver CZ Pendant</t>
+          <t>RL155 Peace Symbol Sterling Silver CZ Pendant</t>
         </is>
       </c>
       <c r="F68" s="12" t="inlineStr"/>
       <c r="G68" s="12" t="inlineStr">
         <is>
-          <t>All Products</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H68" s="12" t="inlineStr"/>
@@ -4431,7 +4313,7 @@
         <v/>
       </c>
       <c r="L68" s="13" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M68" s="10">
         <f>IF(OR(L68="",K68="",L68=0),"",
@@ -4441,11 +4323,7 @@
       <c r="N68" s="11" t="inlineStr"/>
       <c r="O68" s="12" t="inlineStr"/>
       <c r="P68" s="12" t="inlineStr"/>
-      <c r="Q68" s="12" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/12/PhotoRoom-20231218_094646-1.png</t>
-        </is>
-      </c>
+      <c r="Q68" s="12" t="inlineStr"/>
       <c r="R68" s="12" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -4453,7 +4331,7 @@
       </c>
       <c r="S68" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -4461,24 +4339,24 @@
       <c r="A69" s="3" t="inlineStr"/>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>8S8D215724</t>
+          <t>C21C815727</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>15724</t>
+          <t>15727</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr"/>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>R78 Clock Sterling Silver CZ Pendant</t>
+          <t>RL451 Heart Sterling Silver CZ Earrings &amp; Pendant</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr"/>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>All Products</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
@@ -4491,7 +4369,7 @@
         <v/>
       </c>
       <c r="L69" s="9" t="n">
-        <v>280</v>
+        <v>450</v>
       </c>
       <c r="M69" s="10">
         <f>IF(OR(L69="",K69="",L69=0),"",
@@ -4501,11 +4379,7 @@
       <c r="N69" s="11" t="inlineStr"/>
       <c r="O69" s="4" t="inlineStr"/>
       <c r="P69" s="4" t="inlineStr"/>
-      <c r="Q69" s="4" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/12/PhotoRoom-20231218_100123.png</t>
-        </is>
-      </c>
+      <c r="Q69" s="4" t="inlineStr"/>
       <c r="R69" s="4" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -4513,7 +4387,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -4521,24 +4395,24 @@
       <c r="A70" s="3" t="inlineStr"/>
       <c r="B70" s="12" t="inlineStr">
         <is>
-          <t>HXRCG15726</t>
+          <t>12KJ516133-02</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>15726</t>
+          <t>16189</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr"/>
       <c r="E70" s="12" t="inlineStr">
         <is>
-          <t>R701 Infinity Sterling Silver CZ Earrings &amp; Pendant</t>
+          <t>Round Plate Holders - Embossed Studs</t>
         </is>
       </c>
       <c r="F70" s="12" t="inlineStr"/>
       <c r="G70" s="12" t="inlineStr">
         <is>
-          <t>All Products</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H70" s="12" t="inlineStr"/>
@@ -4551,7 +4425,7 @@
         <v/>
       </c>
       <c r="L70" s="13" t="n">
-        <v>430</v>
+        <v>75</v>
       </c>
       <c r="M70" s="10">
         <f>IF(OR(L70="",K70="",L70=0),"",
@@ -4561,11 +4435,7 @@
       <c r="N70" s="11" t="inlineStr"/>
       <c r="O70" s="12" t="inlineStr"/>
       <c r="P70" s="12" t="inlineStr"/>
-      <c r="Q70" s="12" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/12/PhotoRoom-20231218_102046-1.png</t>
-        </is>
-      </c>
+      <c r="Q70" s="12" t="inlineStr"/>
       <c r="R70" s="12" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -4573,7 +4443,7 @@
       </c>
       <c r="S70" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -4581,24 +4451,24 @@
       <c r="A71" s="3" t="inlineStr"/>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>C21C815727</t>
+          <t>8599F12977</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>15727</t>
+          <t>12977</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>RL451 Heart Sterling Silver CZ Earrings &amp; Pendant</t>
+          <t>SCH01 Sterling Silver Chain</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr"/>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>All Products</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr"/>
@@ -4611,7 +4481,7 @@
         <v/>
       </c>
       <c r="L71" s="9" t="n">
-        <v>450</v>
+        <v>250</v>
       </c>
       <c r="M71" s="10">
         <f>IF(OR(L71="",K71="",L71=0),"",
@@ -4621,11 +4491,7 @@
       <c r="N71" s="11" t="inlineStr"/>
       <c r="O71" s="4" t="inlineStr"/>
       <c r="P71" s="4" t="inlineStr"/>
-      <c r="Q71" s="4" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/12/PhotoRoom-20231218_102817.png</t>
-        </is>
-      </c>
+      <c r="Q71" s="4" t="inlineStr"/>
       <c r="R71" s="4" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -4633,7 +4499,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -4641,24 +4507,24 @@
       <c r="A72" s="3" t="inlineStr"/>
       <c r="B72" s="12" t="inlineStr">
         <is>
-          <t>7UTDE15728</t>
+          <t>VJY7V12950</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>15728</t>
+          <t>12950</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr"/>
       <c r="E72" s="12" t="inlineStr">
         <is>
-          <t>Z187 Clover Sterling Silver CZ Earrings &amp; Pendant</t>
+          <t>SZ203 Multicolor CZ Stone Sterling Silver Bracelet</t>
         </is>
       </c>
       <c r="F72" s="12" t="inlineStr"/>
       <c r="G72" s="12" t="inlineStr">
         <is>
-          <t>All Products</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H72" s="12" t="inlineStr"/>
@@ -4671,7 +4537,7 @@
         <v/>
       </c>
       <c r="L72" s="13" t="n">
-        <v>400</v>
+        <v>850</v>
       </c>
       <c r="M72" s="10">
         <f>IF(OR(L72="",K72="",L72=0),"",
@@ -4681,11 +4547,7 @@
       <c r="N72" s="11" t="inlineStr"/>
       <c r="O72" s="12" t="inlineStr"/>
       <c r="P72" s="12" t="inlineStr"/>
-      <c r="Q72" s="12" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/12/PhotoRoom-20231218_103331.png</t>
-        </is>
-      </c>
+      <c r="Q72" s="12" t="inlineStr"/>
       <c r="R72" s="12" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -4693,7 +4555,7 @@
       </c>
       <c r="S72" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -4701,24 +4563,24 @@
       <c r="A73" s="3" t="inlineStr"/>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>M1O9T13589</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>15771</t>
+          <t>13589</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>Sunsign Security Monitoring UPS Power Supply 12V</t>
+          <t>Seige Solo Dress with Studs</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr"/>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>Hardware &gt; Electrical</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
@@ -4731,7 +4593,7 @@
         <v/>
       </c>
       <c r="L73" s="9" t="n">
-        <v>495</v>
+        <v>650</v>
       </c>
       <c r="M73" s="10">
         <f>IF(OR(L73="",K73="",L73=0),"",
@@ -4741,11 +4603,7 @@
       <c r="N73" s="11" t="inlineStr"/>
       <c r="O73" s="4" t="inlineStr"/>
       <c r="P73" s="4" t="inlineStr"/>
-      <c r="Q73" s="4" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/12/PhotoRoom-20231213_072753.png, https://happyharvesting.co.za/wp-content/uploads/2023/12/PhotoRoom-20231213_072753.png, https://happyharvesting.co.za/wp-content/uploads/2023/12/PhotoRoom-20231213_072717.png</t>
-        </is>
-      </c>
+      <c r="Q73" s="4" t="inlineStr"/>
       <c r="R73" s="4" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -4753,7 +4611,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -4761,24 +4619,24 @@
       <c r="A74" s="3" t="inlineStr"/>
       <c r="B74" s="12" t="inlineStr">
         <is>
-          <t>V74CH16111</t>
+          <t>PD8HM13422</t>
         </is>
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>16111</t>
+          <t>13422</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr"/>
       <c r="E74" s="12" t="inlineStr">
         <is>
-          <t>Enchanting Reindeer Crystal Bead Jewelry Mirror Box</t>
+          <t>Stud Dual Black &amp; Shocking Pink</t>
         </is>
       </c>
       <c r="F74" s="12" t="inlineStr"/>
       <c r="G74" s="12" t="inlineStr">
         <is>
-          <t>Homeware &gt; Decor</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H74" s="12" t="inlineStr"/>
@@ -4791,7 +4649,7 @@
         <v/>
       </c>
       <c r="L74" s="13" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="M74" s="10">
         <f>IF(OR(L74="",K74="",L74=0),"",
@@ -4801,11 +4659,7 @@
       <c r="N74" s="11" t="inlineStr"/>
       <c r="O74" s="12" t="inlineStr"/>
       <c r="P74" s="12" t="inlineStr"/>
-      <c r="Q74" s="12" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2023/12/Photo-2023-12-15-13-11-10.jpg, https://happyharvesting.co.za/wp-content/uploads/2023/12/Photo-2023-12-15-13-11-11.jpg, https://happyharvesting.co.za/wp-content/uploads/2023/12/Photo-2023-12-15-13-11-08.jpg</t>
-        </is>
-      </c>
+      <c r="Q74" s="12" t="inlineStr"/>
       <c r="R74" s="12" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -4813,7 +4667,7 @@
       </c>
       <c r="S74" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -4821,24 +4675,24 @@
       <c r="A75" s="3" t="inlineStr"/>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>HU9YU17077</t>
+          <t>M4VGU13418</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>17077</t>
+          <t>13418</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr"/>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>Heart Key Ring</t>
+          <t>Stud Dual Black &amp; White</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr"/>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>Lifestyle &amp; Everyday Essentials</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr"/>
@@ -4851,7 +4705,7 @@
         <v/>
       </c>
       <c r="L75" s="9" t="n">
-        <v>70</v>
+        <v>600</v>
       </c>
       <c r="M75" s="10">
         <f>IF(OR(L75="",K75="",L75=0),"",
@@ -4861,11 +4715,7 @@
       <c r="N75" s="11" t="inlineStr"/>
       <c r="O75" s="4" t="inlineStr"/>
       <c r="P75" s="4" t="inlineStr"/>
-      <c r="Q75" s="4" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2024/01/PhotoRoom-20240121_114853.png</t>
-        </is>
-      </c>
+      <c r="Q75" s="4" t="inlineStr"/>
       <c r="R75" s="4" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -4873,7 +4723,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -4881,24 +4731,24 @@
       <c r="A76" s="3" t="inlineStr"/>
       <c r="B76" s="12" t="inlineStr">
         <is>
-          <t>5JS8X17078</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>17078</t>
+          <t>15771</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr"/>
       <c r="E76" s="12" t="inlineStr">
         <is>
-          <t>Floral Key Ring</t>
+          <t>Sunsign Security Monitoring UPS Power Supply 12V</t>
         </is>
       </c>
       <c r="F76" s="12" t="inlineStr"/>
       <c r="G76" s="12" t="inlineStr">
         <is>
-          <t>Lifestyle &amp; Everyday Essentials</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H76" s="12" t="inlineStr"/>
@@ -4911,7 +4761,7 @@
         <v/>
       </c>
       <c r="L76" s="13" t="n">
-        <v>70</v>
+        <v>495</v>
       </c>
       <c r="M76" s="10">
         <f>IF(OR(L76="",K76="",L76=0),"",
@@ -4921,11 +4771,7 @@
       <c r="N76" s="11" t="inlineStr"/>
       <c r="O76" s="12" t="inlineStr"/>
       <c r="P76" s="12" t="inlineStr"/>
-      <c r="Q76" s="12" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2024/01/PhotoRoom-20240121_114435.png</t>
-        </is>
-      </c>
+      <c r="Q76" s="12" t="inlineStr"/>
       <c r="R76" s="12" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -4933,7 +4779,7 @@
       </c>
       <c r="S76" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -4941,22 +4787,26 @@
       <c r="A77" s="3" t="inlineStr"/>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>F00945</t>
+          <t>U2PK712959</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>18421</t>
+          <t>12959</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr"/>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>Alco Measuring Tape Rubber - 10m</t>
+          <t>TL146 Round Sterling Silver CZ Chain</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr"/>
-      <c r="G77" s="4" t="inlineStr"/>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
       <c r="H77" s="4" t="inlineStr"/>
       <c r="I77" s="6" t="inlineStr"/>
       <c r="J77" s="7" t="n">
@@ -4967,7 +4817,7 @@
         <v/>
       </c>
       <c r="L77" s="9" t="n">
-        <v>190</v>
+        <v>650</v>
       </c>
       <c r="M77" s="10">
         <f>IF(OR(L77="",K77="",L77=0),"",
@@ -4985,7 +4835,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -4993,22 +4843,26 @@
       <c r="A78" s="3" t="inlineStr"/>
       <c r="B78" s="12" t="inlineStr">
         <is>
-          <t>F02210</t>
+          <t>3I91N15714</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>18422</t>
+          <t>15714</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr"/>
       <c r="E78" s="12" t="inlineStr">
         <is>
-          <t>Alco Measuring Tape Rubber - 7.5m</t>
+          <t>X03 CZ Square Stone Tennis Necklace</t>
         </is>
       </c>
       <c r="F78" s="12" t="inlineStr"/>
-      <c r="G78" s="12" t="inlineStr"/>
+      <c r="G78" s="12" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
       <c r="H78" s="12" t="inlineStr"/>
       <c r="I78" s="6" t="inlineStr"/>
       <c r="J78" s="7" t="n">
@@ -5019,7 +4873,7 @@
         <v/>
       </c>
       <c r="L78" s="13" t="n">
-        <v>180</v>
+        <v>2950</v>
       </c>
       <c r="M78" s="10">
         <f>IF(OR(L78="",K78="",L78=0),"",
@@ -5037,7 +4891,7 @@
       </c>
       <c r="S78" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -5045,22 +4899,26 @@
       <c r="A79" s="3" t="inlineStr"/>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>F00944</t>
+          <t>996A115690</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>18423</t>
+          <t>15690</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr"/>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>Alco Measuring Tape Rubber - 5m</t>
+          <t>X07 CZ Baguette Tennis Bracelet</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr"/>
-      <c r="G79" s="4" t="inlineStr"/>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
       <c r="H79" s="4" t="inlineStr"/>
       <c r="I79" s="6" t="inlineStr"/>
       <c r="J79" s="7" t="n">
@@ -5071,7 +4929,7 @@
         <v/>
       </c>
       <c r="L79" s="9" t="n">
-        <v>170</v>
+        <v>1100</v>
       </c>
       <c r="M79" s="10">
         <f>IF(OR(L79="",K79="",L79=0),"",
@@ -5089,7 +4947,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -5097,22 +4955,26 @@
       <c r="A80" s="3" t="inlineStr"/>
       <c r="B80" s="12" t="inlineStr">
         <is>
-          <t>F00943</t>
+          <t>ALY9V15693</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>18424</t>
+          <t>15693</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr"/>
       <c r="E80" s="12" t="inlineStr">
         <is>
-          <t>Alco Measuring Tape Rubber - 3m</t>
+          <t>X09 Snake CZ Tennis Bracelet</t>
         </is>
       </c>
       <c r="F80" s="12" t="inlineStr"/>
-      <c r="G80" s="12" t="inlineStr"/>
+      <c r="G80" s="12" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
       <c r="H80" s="12" t="inlineStr"/>
       <c r="I80" s="6" t="inlineStr"/>
       <c r="J80" s="7" t="n">
@@ -5123,7 +4985,7 @@
         <v/>
       </c>
       <c r="L80" s="13" t="n">
-        <v>160</v>
+        <v>950</v>
       </c>
       <c r="M80" s="10">
         <f>IF(OR(L80="",K80="",L80=0),"",
@@ -5141,7 +5003,7 @@
       </c>
       <c r="S80" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -5149,22 +5011,26 @@
       <c r="A81" s="3" t="inlineStr"/>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>F00942</t>
+          <t>T8D7Y15712</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>18426</t>
+          <t>15712</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr"/>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>Alco Measuring Tape Plastic - 10m</t>
+          <t>X15 Morse CZ Tennis Bracelet</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr"/>
-      <c r="G81" s="4" t="inlineStr"/>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
       <c r="H81" s="4" t="inlineStr"/>
       <c r="I81" s="6" t="inlineStr"/>
       <c r="J81" s="7" t="n">
@@ -5175,7 +5041,7 @@
         <v/>
       </c>
       <c r="L81" s="9" t="n">
-        <v>220</v>
+        <v>950</v>
       </c>
       <c r="M81" s="10">
         <f>IF(OR(L81="",K81="",L81=0),"",
@@ -5193,7 +5059,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -5201,22 +5067,26 @@
       <c r="A82" s="3" t="inlineStr"/>
       <c r="B82" s="12" t="inlineStr">
         <is>
-          <t>F00941</t>
+          <t>LUZ5U15694</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>18427</t>
+          <t>15694</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr"/>
       <c r="E82" s="12" t="inlineStr">
         <is>
-          <t>Alco Measuring Tape Plastic - 5m</t>
+          <t>X16 Round Delicate CZ Tennis Bracelet</t>
         </is>
       </c>
       <c r="F82" s="12" t="inlineStr"/>
-      <c r="G82" s="12" t="inlineStr"/>
+      <c r="G82" s="12" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
       <c r="H82" s="12" t="inlineStr"/>
       <c r="I82" s="6" t="inlineStr"/>
       <c r="J82" s="7" t="n">
@@ -5227,7 +5097,7 @@
         <v/>
       </c>
       <c r="L82" s="13" t="n">
-        <v>150</v>
+        <v>800</v>
       </c>
       <c r="M82" s="10">
         <f>IF(OR(L82="",K82="",L82=0),"",
@@ -5245,7 +5115,7 @@
       </c>
       <c r="S82" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -5253,22 +5123,26 @@
       <c r="A83" s="3" t="inlineStr"/>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>F00940</t>
+          <t>GKB3515695</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>18428</t>
+          <t>15695</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr"/>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>Alco Measuring Tape Plastic - 3m</t>
+          <t>X19 Teardrop CZ Tennis Bracelet</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr"/>
-      <c r="G83" s="4" t="inlineStr"/>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
       <c r="H83" s="4" t="inlineStr"/>
       <c r="I83" s="6" t="inlineStr"/>
       <c r="J83" s="7" t="n">
@@ -5279,7 +5153,7 @@
         <v/>
       </c>
       <c r="L83" s="9" t="n">
-        <v>140</v>
+        <v>1200</v>
       </c>
       <c r="M83" s="10">
         <f>IF(OR(L83="",K83="",L83=0),"",
@@ -5297,7 +5171,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -5305,24 +5179,24 @@
       <c r="A84" s="3" t="inlineStr"/>
       <c r="B84" s="12" t="inlineStr">
         <is>
-          <t>7IB5W20260</t>
+          <t>LC39F15711</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>20260</t>
+          <t>15711</t>
         </is>
       </c>
       <c r="D84" s="12" t="inlineStr"/>
       <c r="E84" s="12" t="inlineStr">
         <is>
-          <t>Luxury Peel And Stick Flooring Tiles - F01813</t>
+          <t>X21 Slabbed CZ Tennis Bracelet</t>
         </is>
       </c>
       <c r="F84" s="12" t="inlineStr"/>
       <c r="G84" s="12" t="inlineStr">
         <is>
-          <t>Hardware &gt; Peel and Stick Tiles &gt; Luxury Vinyl Peel &amp; Stick Tiles</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H84" s="12" t="inlineStr"/>
@@ -5335,7 +5209,7 @@
         <v/>
       </c>
       <c r="L84" s="13" t="n">
-        <v>580</v>
+        <v>1500</v>
       </c>
       <c r="M84" s="10">
         <f>IF(OR(L84="",K84="",L84=0),"",
@@ -5345,11 +5219,7 @@
       <c r="N84" s="11" t="inlineStr"/>
       <c r="O84" s="12" t="inlineStr"/>
       <c r="P84" s="12" t="inlineStr"/>
-      <c r="Q84" s="12" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2024/04/tassy-choc-f01813-Photoroom.jpg</t>
-        </is>
-      </c>
+      <c r="Q84" s="12" t="inlineStr"/>
       <c r="R84" s="12" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -5357,7 +5227,7 @@
       </c>
       <c r="S84" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -5365,24 +5235,24 @@
       <c r="A85" s="3" t="inlineStr"/>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>7IB5W20260-1</t>
+          <t>UM73O15692</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>20269</t>
+          <t>15692</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr"/>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>Luxury Peel And Stick Flooring Tiles - F01810</t>
+          <t>X23 Round CZ Tennis Bracelet</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr"/>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>Hardware &gt; Peel and Stick Tiles &gt; Luxury Vinyl Peel &amp; Stick Tiles</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr"/>
@@ -5395,7 +5265,7 @@
         <v/>
       </c>
       <c r="L85" s="9" t="n">
-        <v>580</v>
+        <v>1200</v>
       </c>
       <c r="M85" s="10">
         <f>IF(OR(L85="",K85="",L85=0),"",
@@ -5405,11 +5275,7 @@
       <c r="N85" s="11" t="inlineStr"/>
       <c r="O85" s="4" t="inlineStr"/>
       <c r="P85" s="4" t="inlineStr"/>
-      <c r="Q85" s="4" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2024/04/tassy-ash-f01810-Photoroom.jpg</t>
-        </is>
-      </c>
+      <c r="Q85" s="4" t="inlineStr"/>
       <c r="R85" s="4" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -5417,7 +5283,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -5425,24 +5291,24 @@
       <c r="A86" s="3" t="inlineStr"/>
       <c r="B86" s="12" t="inlineStr">
         <is>
-          <t>7IB5W20260-1-1</t>
+          <t>747RC15691</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>20270</t>
+          <t>15691</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr"/>
       <c r="E86" s="12" t="inlineStr">
         <is>
-          <t>Luxury Peel And Stick Flooring Tiles - F01804</t>
+          <t>X28 CZ Tennis Bracelet</t>
         </is>
       </c>
       <c r="F86" s="12" t="inlineStr"/>
       <c r="G86" s="12" t="inlineStr">
         <is>
-          <t>Hardware &gt; Peel and Stick Tiles &gt; Luxury Vinyl Peel &amp; Stick Tiles</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H86" s="12" t="inlineStr"/>
@@ -5455,7 +5321,7 @@
         <v/>
       </c>
       <c r="L86" s="13" t="n">
-        <v>580</v>
+        <v>1200</v>
       </c>
       <c r="M86" s="10">
         <f>IF(OR(L86="",K86="",L86=0),"",
@@ -5465,11 +5331,7 @@
       <c r="N86" s="11" t="inlineStr"/>
       <c r="O86" s="12" t="inlineStr"/>
       <c r="P86" s="12" t="inlineStr"/>
-      <c r="Q86" s="12" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2024/04/tassy-brown-woodf01804-Photoroom.jpg</t>
-        </is>
-      </c>
+      <c r="Q86" s="12" t="inlineStr"/>
       <c r="R86" s="12" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -5477,7 +5339,7 @@
       </c>
       <c r="S86" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -5485,24 +5347,24 @@
       <c r="A87" s="3" t="inlineStr"/>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>7IB5W20260-1-1-1</t>
+          <t>UOC3X12952</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>20271</t>
+          <t>12952</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr"/>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>Luxury Peel And Stick Flooring Tiles - F01805</t>
+          <t>Z01 Black CZ Sterling Silver Tennis Bracelet</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr"/>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>Hardware &gt; Peel and Stick Tiles &gt; Luxury Vinyl Peel &amp; Stick Tiles</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr"/>
@@ -5515,7 +5377,7 @@
         <v/>
       </c>
       <c r="L87" s="9" t="n">
-        <v>580</v>
+        <v>450</v>
       </c>
       <c r="M87" s="10">
         <f>IF(OR(L87="",K87="",L87=0),"",
@@ -5525,11 +5387,7 @@
       <c r="N87" s="11" t="inlineStr"/>
       <c r="O87" s="4" t="inlineStr"/>
       <c r="P87" s="4" t="inlineStr"/>
-      <c r="Q87" s="4" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2024/04/tasst-stone-f01805-Photoroom.jpg</t>
-        </is>
-      </c>
+      <c r="Q87" s="4" t="inlineStr"/>
       <c r="R87" s="4" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -5537,7 +5395,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -5545,24 +5403,24 @@
       <c r="A88" s="3" t="inlineStr"/>
       <c r="B88" s="12" t="inlineStr">
         <is>
-          <t>7IB5W20260-1-1-1-1</t>
+          <t>LK8BE13198</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>20272</t>
+          <t>13198</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr"/>
       <c r="E88" s="12" t="inlineStr">
         <is>
-          <t>Luxury Peel And Stick Flooring Tiles - F01812</t>
+          <t>Z107 Sterling Silver CZ Ring</t>
         </is>
       </c>
       <c r="F88" s="12" t="inlineStr"/>
       <c r="G88" s="12" t="inlineStr">
         <is>
-          <t>Hardware &gt; Peel and Stick Tiles &gt; Luxury Vinyl Peel &amp; Stick Tiles</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H88" s="12" t="inlineStr"/>
@@ -5575,7 +5433,7 @@
         <v/>
       </c>
       <c r="L88" s="13" t="n">
-        <v>580</v>
+        <v>390</v>
       </c>
       <c r="M88" s="10">
         <f>IF(OR(L88="",K88="",L88=0),"",
@@ -5585,11 +5443,7 @@
       <c r="N88" s="11" t="inlineStr"/>
       <c r="O88" s="12" t="inlineStr"/>
       <c r="P88" s="12" t="inlineStr"/>
-      <c r="Q88" s="12" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2024/04/tassy-brown-f01812-Photoroom.jpg</t>
-        </is>
-      </c>
+      <c r="Q88" s="12" t="inlineStr"/>
       <c r="R88" s="12" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -5597,7 +5451,7 @@
       </c>
       <c r="S88" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -5605,24 +5459,24 @@
       <c r="A89" s="3" t="inlineStr"/>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>7IB5W20260-1-1-1-1-1</t>
+          <t>2W4VQ15722</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>20273</t>
+          <t>15722</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr"/>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>Luxury Peel And Stick Flooring Tiles - F01807</t>
+          <t>Z116 Twin Tails Heart Sterling Silver CZ Pendant</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr"/>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>Hardware &gt; Peel and Stick Tiles &gt; Luxury Vinyl Peel &amp; Stick Tiles</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr"/>
@@ -5635,7 +5489,7 @@
         <v/>
       </c>
       <c r="L89" s="9" t="n">
-        <v>580</v>
+        <v>180</v>
       </c>
       <c r="M89" s="10">
         <f>IF(OR(L89="",K89="",L89=0),"",
@@ -5645,11 +5499,7 @@
       <c r="N89" s="11" t="inlineStr"/>
       <c r="O89" s="4" t="inlineStr"/>
       <c r="P89" s="4" t="inlineStr"/>
-      <c r="Q89" s="4" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2024/04/Tassy-bronze-Photoroom.jpg</t>
-        </is>
-      </c>
+      <c r="Q89" s="4" t="inlineStr"/>
       <c r="R89" s="4" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -5657,7 +5507,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -5665,24 +5515,24 @@
       <c r="A90" s="3" t="inlineStr"/>
       <c r="B90" s="12" t="inlineStr">
         <is>
-          <t>7IB5W20260-1-1-1-1-1-1</t>
+          <t>7UTDE15728</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>20274</t>
+          <t>15728</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr"/>
       <c r="E90" s="12" t="inlineStr">
         <is>
-          <t>Luxury Peel And Stick Flooring Tiles - F01808</t>
+          <t>Z187 Clover Sterling Silver CZ Earrings &amp; Pendant</t>
         </is>
       </c>
       <c r="F90" s="12" t="inlineStr"/>
       <c r="G90" s="12" t="inlineStr">
         <is>
-          <t>Hardware &gt; Peel and Stick Tiles &gt; Luxury Vinyl Peel &amp; Stick Tiles</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H90" s="12" t="inlineStr"/>
@@ -5695,7 +5545,7 @@
         <v/>
       </c>
       <c r="L90" s="13" t="n">
-        <v>580</v>
+        <v>400</v>
       </c>
       <c r="M90" s="10">
         <f>IF(OR(L90="",K90="",L90=0),"",
@@ -5705,11 +5555,7 @@
       <c r="N90" s="11" t="inlineStr"/>
       <c r="O90" s="12" t="inlineStr"/>
       <c r="P90" s="12" t="inlineStr"/>
-      <c r="Q90" s="12" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2024/04/tassy-baige-fo1808-Photoroom.jpg</t>
-        </is>
-      </c>
+      <c r="Q90" s="12" t="inlineStr"/>
       <c r="R90" s="12" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -5717,7 +5563,7 @@
       </c>
       <c r="S90" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -5725,24 +5571,24 @@
       <c r="A91" s="3" t="inlineStr"/>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>7IB5W20260-1-1-1-1-1-1-1</t>
+          <t>P477412965</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>20275</t>
+          <t>12965</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr"/>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>Luxury Peel And Stick Flooring Tiles - F01809</t>
+          <t>Z247 Round Sterling Silver CZ Blue Stud Earrings</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr"/>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>Hardware &gt; Peel and Stick Tiles &gt; Luxury Vinyl Peel &amp; Stick Tiles</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr"/>
@@ -5755,7 +5601,7 @@
         <v/>
       </c>
       <c r="L91" s="9" t="n">
-        <v>580</v>
+        <v>300</v>
       </c>
       <c r="M91" s="10">
         <f>IF(OR(L91="",K91="",L91=0),"",
@@ -5765,11 +5611,7 @@
       <c r="N91" s="11" t="inlineStr"/>
       <c r="O91" s="4" t="inlineStr"/>
       <c r="P91" s="4" t="inlineStr"/>
-      <c r="Q91" s="4" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2024/04/tassy-grey-f01809-Photoroom.jpg</t>
-        </is>
-      </c>
+      <c r="Q91" s="4" t="inlineStr"/>
       <c r="R91" s="4" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -5777,7 +5619,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -5785,24 +5627,24 @@
       <c r="A92" s="3" t="inlineStr"/>
       <c r="B92" s="12" t="inlineStr">
         <is>
-          <t>F02251</t>
+          <t>UKQ6912953</t>
         </is>
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>32245</t>
+          <t>12953</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr"/>
       <c r="E92" s="12" t="inlineStr">
         <is>
-          <t>Catering Table - Black</t>
+          <t>Z44 Sterling Silver Bracelet With Pink CZ</t>
         </is>
       </c>
       <c r="F92" s="12" t="inlineStr"/>
       <c r="G92" s="12" t="inlineStr">
         <is>
-          <t>Homeware &gt; Decor &gt; Kitchen &amp; Table Accessories</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H92" s="12" t="inlineStr"/>
@@ -5814,7 +5656,9 @@
         <f>IF(I92="","",I92*(1+J92/100))</f>
         <v/>
       </c>
-      <c r="L92" s="6" t="inlineStr"/>
+      <c r="L92" s="13" t="n">
+        <v>800</v>
+      </c>
       <c r="M92" s="10">
         <f>IF(OR(L92="",K92="",L92=0),"",
   (L92-K92)/L92*100)</f>
@@ -5823,11 +5667,7 @@
       <c r="N92" s="11" t="inlineStr"/>
       <c r="O92" s="12" t="inlineStr"/>
       <c r="P92" s="12" t="inlineStr"/>
-      <c r="Q92" s="12" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2025/04/Folding-table.png, https://happyharvesting.co.za/wp-content/uploads/2025/04/table.jpg</t>
-        </is>
-      </c>
+      <c r="Q92" s="12" t="inlineStr"/>
       <c r="R92" s="12" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -5835,7 +5675,7 @@
       </c>
       <c r="S92" s="12" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
@@ -5843,24 +5683,24 @@
       <c r="A93" s="3" t="inlineStr"/>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>F00417</t>
+          <t>2D7BV12954</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>32248</t>
+          <t>12954</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr"/>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>Catering Table - White</t>
+          <t>Z506 Sterling Dome Silver Ring</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr"/>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>Homeware &gt; Kitchenware</t>
+          <t>Jewellery</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
@@ -5873,7 +5713,7 @@
         <v/>
       </c>
       <c r="L93" s="9" t="n">
-        <v>399</v>
+        <v>650</v>
       </c>
       <c r="M93" s="10">
         <f>IF(OR(L93="",K93="",L93=0),"",
@@ -5883,11 +5723,7 @@
       <c r="N93" s="11" t="inlineStr"/>
       <c r="O93" s="4" t="inlineStr"/>
       <c r="P93" s="4" t="inlineStr"/>
-      <c r="Q93" s="4" t="inlineStr">
-        <is>
-          <t>https://happyharvesting.co.za/wp-content/uploads/2025/04/Folding-table.png, https://happyharvesting.co.za/wp-content/uploads/2025/04/table.jpg</t>
-        </is>
-      </c>
+      <c r="Q93" s="4" t="inlineStr"/>
       <c r="R93" s="4" t="inlineStr">
         <is>
           <t>2026-03-12</t>
@@ -5895,20 +5731,36 @@
       </c>
       <c r="S93" s="4" t="inlineStr">
         <is>
-          <t>Pre-loaded from WC export — fill in cost price</t>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="3" t="n"/>
-      <c r="B94" s="4" t="n"/>
-      <c r="C94" s="4" t="n"/>
-      <c r="D94" s="4" t="n"/>
-      <c r="E94" s="3" t="n"/>
-      <c r="F94" s="4" t="n"/>
-      <c r="G94" s="4" t="n"/>
-      <c r="H94" s="4" t="n"/>
-      <c r="I94" s="3" t="n"/>
+      <c r="A94" s="3" t="inlineStr"/>
+      <c r="B94" s="12" t="inlineStr">
+        <is>
+          <t>OW22115716</t>
+        </is>
+      </c>
+      <c r="C94" s="12" t="inlineStr">
+        <is>
+          <t>15716</t>
+        </is>
+      </c>
+      <c r="D94" s="12" t="inlineStr"/>
+      <c r="E94" s="12" t="inlineStr">
+        <is>
+          <t>Z61 Tree Sterling Silver CZ Pendant</t>
+        </is>
+      </c>
+      <c r="F94" s="12" t="inlineStr"/>
+      <c r="G94" s="12" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
+      <c r="H94" s="12" t="inlineStr"/>
+      <c r="I94" s="6" t="inlineStr"/>
       <c r="J94" s="7" t="n">
         <v>15</v>
       </c>
@@ -5916,29 +5768,55 @@
         <f>IF(I94="","",I94*(1+J94/100))</f>
         <v/>
       </c>
-      <c r="L94" s="3" t="n"/>
+      <c r="L94" s="13" t="n">
+        <v>300</v>
+      </c>
       <c r="M94" s="10">
         <f>IF(OR(L94="",K94="",L94=0),"",
   (L94-K94)/L94*100)</f>
         <v/>
       </c>
-      <c r="N94" s="3" t="n"/>
-      <c r="O94" s="4" t="n"/>
-      <c r="P94" s="4" t="n"/>
-      <c r="Q94" s="4" t="n"/>
-      <c r="R94" s="4" t="n"/>
-      <c r="S94" s="4" t="n"/>
+      <c r="N94" s="11" t="inlineStr"/>
+      <c r="O94" s="12" t="inlineStr"/>
+      <c r="P94" s="12" t="inlineStr"/>
+      <c r="Q94" s="12" t="inlineStr"/>
+      <c r="R94" s="12" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="S94" s="12" t="inlineStr">
+        <is>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
+        </is>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" s="3" t="n"/>
-      <c r="B95" s="12" t="n"/>
-      <c r="C95" s="12" t="n"/>
-      <c r="D95" s="12" t="n"/>
-      <c r="E95" s="3" t="n"/>
-      <c r="F95" s="12" t="n"/>
-      <c r="G95" s="12" t="n"/>
-      <c r="H95" s="12" t="n"/>
-      <c r="I95" s="3" t="n"/>
+      <c r="A95" s="3" t="inlineStr"/>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>969M212955</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>12955</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr"/>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>Z69 Multicolor CZ Hoop Sterling Silver Earrings</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr"/>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
+      <c r="H95" s="4" t="inlineStr"/>
+      <c r="I95" s="6" t="inlineStr"/>
       <c r="J95" s="7" t="n">
         <v>15</v>
       </c>
@@ -5946,29 +5824,55 @@
         <f>IF(I95="","",I95*(1+J95/100))</f>
         <v/>
       </c>
-      <c r="L95" s="3" t="n"/>
+      <c r="L95" s="9" t="n">
+        <v>1200</v>
+      </c>
       <c r="M95" s="10">
         <f>IF(OR(L95="",K95="",L95=0),"",
   (L95-K95)/L95*100)</f>
         <v/>
       </c>
-      <c r="N95" s="3" t="n"/>
-      <c r="O95" s="12" t="n"/>
-      <c r="P95" s="12" t="n"/>
-      <c r="Q95" s="12" t="n"/>
-      <c r="R95" s="12" t="n"/>
-      <c r="S95" s="12" t="n"/>
+      <c r="N95" s="11" t="inlineStr"/>
+      <c r="O95" s="4" t="inlineStr"/>
+      <c r="P95" s="4" t="inlineStr"/>
+      <c r="Q95" s="4" t="inlineStr"/>
+      <c r="R95" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="S95" s="4" t="inlineStr">
+        <is>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
+        </is>
+      </c>
     </row>
     <row r="96">
-      <c r="A96" s="3" t="n"/>
-      <c r="B96" s="4" t="n"/>
-      <c r="C96" s="4" t="n"/>
-      <c r="D96" s="4" t="n"/>
-      <c r="E96" s="3" t="n"/>
-      <c r="F96" s="4" t="n"/>
-      <c r="G96" s="4" t="n"/>
-      <c r="H96" s="4" t="n"/>
-      <c r="I96" s="3" t="n"/>
+      <c r="A96" s="3" t="inlineStr"/>
+      <c r="B96" s="12" t="inlineStr">
+        <is>
+          <t>5ENH612951</t>
+        </is>
+      </c>
+      <c r="C96" s="12" t="inlineStr">
+        <is>
+          <t>12951</t>
+        </is>
+      </c>
+      <c r="D96" s="12" t="inlineStr"/>
+      <c r="E96" s="12" t="inlineStr">
+        <is>
+          <t>Z71 Multicolor CZ Sterling Silver Ring</t>
+        </is>
+      </c>
+      <c r="F96" s="12" t="inlineStr"/>
+      <c r="G96" s="12" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
+      <c r="H96" s="12" t="inlineStr"/>
+      <c r="I96" s="6" t="inlineStr"/>
       <c r="J96" s="7" t="n">
         <v>15</v>
       </c>
@@ -5976,29 +5880,55 @@
         <f>IF(I96="","",I96*(1+J96/100))</f>
         <v/>
       </c>
-      <c r="L96" s="3" t="n"/>
+      <c r="L96" s="13" t="n">
+        <v>550</v>
+      </c>
       <c r="M96" s="10">
         <f>IF(OR(L96="",K96="",L96=0),"",
   (L96-K96)/L96*100)</f>
         <v/>
       </c>
-      <c r="N96" s="3" t="n"/>
-      <c r="O96" s="4" t="n"/>
-      <c r="P96" s="4" t="n"/>
-      <c r="Q96" s="4" t="n"/>
-      <c r="R96" s="4" t="n"/>
-      <c r="S96" s="4" t="n"/>
+      <c r="N96" s="11" t="inlineStr"/>
+      <c r="O96" s="12" t="inlineStr"/>
+      <c r="P96" s="12" t="inlineStr"/>
+      <c r="Q96" s="12" t="inlineStr"/>
+      <c r="R96" s="12" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="S96" s="12" t="inlineStr">
+        <is>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
+        </is>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="n"/>
-      <c r="B97" s="12" t="n"/>
-      <c r="C97" s="12" t="n"/>
-      <c r="D97" s="12" t="n"/>
-      <c r="E97" s="3" t="n"/>
-      <c r="F97" s="12" t="n"/>
-      <c r="G97" s="12" t="n"/>
-      <c r="H97" s="12" t="n"/>
-      <c r="I97" s="3" t="n"/>
+      <c r="A97" s="3" t="inlineStr"/>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>894NH12964</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>12964</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr"/>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>Z746 Sterling Silver Purple CZ Studs</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr"/>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
+      <c r="H97" s="4" t="inlineStr"/>
+      <c r="I97" s="6" t="inlineStr"/>
       <c r="J97" s="7" t="n">
         <v>15</v>
       </c>
@@ -6006,29 +5936,55 @@
         <f>IF(I97="","",I97*(1+J97/100))</f>
         <v/>
       </c>
-      <c r="L97" s="3" t="n"/>
+      <c r="L97" s="9" t="n">
+        <v>300</v>
+      </c>
       <c r="M97" s="10">
         <f>IF(OR(L97="",K97="",L97=0),"",
   (L97-K97)/L97*100)</f>
         <v/>
       </c>
-      <c r="N97" s="3" t="n"/>
-      <c r="O97" s="12" t="n"/>
-      <c r="P97" s="12" t="n"/>
-      <c r="Q97" s="12" t="n"/>
-      <c r="R97" s="12" t="n"/>
-      <c r="S97" s="12" t="n"/>
+      <c r="N97" s="11" t="inlineStr"/>
+      <c r="O97" s="4" t="inlineStr"/>
+      <c r="P97" s="4" t="inlineStr"/>
+      <c r="Q97" s="4" t="inlineStr"/>
+      <c r="R97" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="S97" s="4" t="inlineStr">
+        <is>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
+        </is>
+      </c>
     </row>
     <row r="98">
-      <c r="A98" s="3" t="n"/>
-      <c r="B98" s="4" t="n"/>
-      <c r="C98" s="4" t="n"/>
-      <c r="D98" s="4" t="n"/>
-      <c r="E98" s="3" t="n"/>
-      <c r="F98" s="4" t="n"/>
-      <c r="G98" s="4" t="n"/>
-      <c r="H98" s="4" t="n"/>
-      <c r="I98" s="3" t="n"/>
+      <c r="A98" s="3" t="inlineStr"/>
+      <c r="B98" s="12" t="inlineStr">
+        <is>
+          <t>JD25O15718</t>
+        </is>
+      </c>
+      <c r="C98" s="12" t="inlineStr">
+        <is>
+          <t>15718</t>
+        </is>
+      </c>
+      <c r="D98" s="12" t="inlineStr"/>
+      <c r="E98" s="12" t="inlineStr">
+        <is>
+          <t>Z91 Double Heart Sterling Silver CZ Pendant</t>
+        </is>
+      </c>
+      <c r="F98" s="12" t="inlineStr"/>
+      <c r="G98" s="12" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
+      <c r="H98" s="12" t="inlineStr"/>
+      <c r="I98" s="6" t="inlineStr"/>
       <c r="J98" s="7" t="n">
         <v>15</v>
       </c>
@@ -6036,29 +5992,55 @@
         <f>IF(I98="","",I98*(1+J98/100))</f>
         <v/>
       </c>
-      <c r="L98" s="3" t="n"/>
+      <c r="L98" s="13" t="n">
+        <v>250</v>
+      </c>
       <c r="M98" s="10">
         <f>IF(OR(L98="",K98="",L98=0),"",
   (L98-K98)/L98*100)</f>
         <v/>
       </c>
-      <c r="N98" s="3" t="n"/>
-      <c r="O98" s="4" t="n"/>
-      <c r="P98" s="4" t="n"/>
-      <c r="Q98" s="4" t="n"/>
-      <c r="R98" s="4" t="n"/>
-      <c r="S98" s="4" t="n"/>
+      <c r="N98" s="11" t="inlineStr"/>
+      <c r="O98" s="12" t="inlineStr"/>
+      <c r="P98" s="12" t="inlineStr"/>
+      <c r="Q98" s="12" t="inlineStr"/>
+      <c r="R98" s="12" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="S98" s="12" t="inlineStr">
+        <is>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
+        </is>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" s="3" t="n"/>
-      <c r="B99" s="12" t="n"/>
-      <c r="C99" s="12" t="n"/>
-      <c r="D99" s="12" t="n"/>
-      <c r="E99" s="3" t="n"/>
-      <c r="F99" s="12" t="n"/>
-      <c r="G99" s="12" t="n"/>
-      <c r="H99" s="12" t="n"/>
-      <c r="I99" s="3" t="n"/>
+      <c r="A99" s="3" t="inlineStr"/>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>3YW8S15715</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>15715</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr"/>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>Z92 Round Sterling Silver CZ Pendant</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr"/>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
+      <c r="H99" s="4" t="inlineStr"/>
+      <c r="I99" s="6" t="inlineStr"/>
       <c r="J99" s="7" t="n">
         <v>15</v>
       </c>
@@ -6066,29 +6048,55 @@
         <f>IF(I99="","",I99*(1+J99/100))</f>
         <v/>
       </c>
-      <c r="L99" s="3" t="n"/>
+      <c r="L99" s="9" t="n">
+        <v>150</v>
+      </c>
       <c r="M99" s="10">
         <f>IF(OR(L99="",K99="",L99=0),"",
   (L99-K99)/L99*100)</f>
         <v/>
       </c>
-      <c r="N99" s="3" t="n"/>
-      <c r="O99" s="12" t="n"/>
-      <c r="P99" s="12" t="n"/>
-      <c r="Q99" s="12" t="n"/>
-      <c r="R99" s="12" t="n"/>
-      <c r="S99" s="12" t="n"/>
+      <c r="N99" s="11" t="inlineStr"/>
+      <c r="O99" s="4" t="inlineStr"/>
+      <c r="P99" s="4" t="inlineStr"/>
+      <c r="Q99" s="4" t="inlineStr"/>
+      <c r="R99" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="S99" s="4" t="inlineStr">
+        <is>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" s="3" t="n"/>
-      <c r="B100" s="4" t="n"/>
-      <c r="C100" s="4" t="n"/>
-      <c r="D100" s="4" t="n"/>
-      <c r="E100" s="3" t="n"/>
-      <c r="F100" s="4" t="n"/>
-      <c r="G100" s="4" t="n"/>
-      <c r="H100" s="4" t="n"/>
-      <c r="I100" s="3" t="n"/>
+      <c r="A100" s="3" t="inlineStr"/>
+      <c r="B100" s="12" t="inlineStr">
+        <is>
+          <t>7BGS712948</t>
+        </is>
+      </c>
+      <c r="C100" s="12" t="inlineStr">
+        <is>
+          <t>12948</t>
+        </is>
+      </c>
+      <c r="D100" s="12" t="inlineStr"/>
+      <c r="E100" s="12" t="inlineStr">
+        <is>
+          <t>Z93 Teardrop Sterling Silver CZ Pendant</t>
+        </is>
+      </c>
+      <c r="F100" s="12" t="inlineStr"/>
+      <c r="G100" s="12" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
+      <c r="H100" s="12" t="inlineStr"/>
+      <c r="I100" s="6" t="inlineStr"/>
       <c r="J100" s="7" t="n">
         <v>15</v>
       </c>
@@ -6096,28 +6104,38 @@
         <f>IF(I100="","",I100*(1+J100/100))</f>
         <v/>
       </c>
-      <c r="L100" s="3" t="n"/>
+      <c r="L100" s="13" t="n">
+        <v>200</v>
+      </c>
       <c r="M100" s="10">
         <f>IF(OR(L100="",K100="",L100=0),"",
   (L100-K100)/L100*100)</f>
         <v/>
       </c>
-      <c r="N100" s="3" t="n"/>
-      <c r="O100" s="4" t="n"/>
-      <c r="P100" s="4" t="n"/>
-      <c r="Q100" s="4" t="n"/>
-      <c r="R100" s="4" t="n"/>
-      <c r="S100" s="4" t="n"/>
+      <c r="N100" s="11" t="inlineStr"/>
+      <c r="O100" s="12" t="inlineStr"/>
+      <c r="P100" s="12" t="inlineStr"/>
+      <c r="Q100" s="12" t="inlineStr"/>
+      <c r="R100" s="12" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="S100" s="12" t="inlineStr">
+        <is>
+          <t>★ Selling price on WC — FILL IN COST PRICE</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n"/>
-      <c r="B101" s="12" t="n"/>
-      <c r="C101" s="12" t="n"/>
-      <c r="D101" s="12" t="n"/>
+      <c r="B101" s="4" t="n"/>
+      <c r="C101" s="4" t="n"/>
+      <c r="D101" s="4" t="n"/>
       <c r="E101" s="3" t="n"/>
-      <c r="F101" s="12" t="n"/>
-      <c r="G101" s="12" t="n"/>
-      <c r="H101" s="12" t="n"/>
+      <c r="F101" s="4" t="n"/>
+      <c r="G101" s="4" t="n"/>
+      <c r="H101" s="4" t="n"/>
       <c r="I101" s="3" t="n"/>
       <c r="J101" s="7" t="n">
         <v>15</v>
@@ -6133,21 +6151,21 @@
         <v/>
       </c>
       <c r="N101" s="3" t="n"/>
-      <c r="O101" s="12" t="n"/>
-      <c r="P101" s="12" t="n"/>
-      <c r="Q101" s="12" t="n"/>
-      <c r="R101" s="12" t="n"/>
-      <c r="S101" s="12" t="n"/>
+      <c r="O101" s="4" t="n"/>
+      <c r="P101" s="4" t="n"/>
+      <c r="Q101" s="4" t="n"/>
+      <c r="R101" s="4" t="n"/>
+      <c r="S101" s="4" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n"/>
-      <c r="B102" s="4" t="n"/>
-      <c r="C102" s="4" t="n"/>
-      <c r="D102" s="4" t="n"/>
+      <c r="B102" s="12" t="n"/>
+      <c r="C102" s="12" t="n"/>
+      <c r="D102" s="12" t="n"/>
       <c r="E102" s="3" t="n"/>
-      <c r="F102" s="4" t="n"/>
-      <c r="G102" s="4" t="n"/>
-      <c r="H102" s="4" t="n"/>
+      <c r="F102" s="12" t="n"/>
+      <c r="G102" s="12" t="n"/>
+      <c r="H102" s="12" t="n"/>
       <c r="I102" s="3" t="n"/>
       <c r="J102" s="7" t="n">
         <v>15</v>
@@ -6163,21 +6181,21 @@
         <v/>
       </c>
       <c r="N102" s="3" t="n"/>
-      <c r="O102" s="4" t="n"/>
-      <c r="P102" s="4" t="n"/>
-      <c r="Q102" s="4" t="n"/>
-      <c r="R102" s="4" t="n"/>
-      <c r="S102" s="4" t="n"/>
+      <c r="O102" s="12" t="n"/>
+      <c r="P102" s="12" t="n"/>
+      <c r="Q102" s="12" t="n"/>
+      <c r="R102" s="12" t="n"/>
+      <c r="S102" s="12" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n"/>
-      <c r="B103" s="12" t="n"/>
-      <c r="C103" s="12" t="n"/>
-      <c r="D103" s="12" t="n"/>
+      <c r="B103" s="4" t="n"/>
+      <c r="C103" s="4" t="n"/>
+      <c r="D103" s="4" t="n"/>
       <c r="E103" s="3" t="n"/>
-      <c r="F103" s="12" t="n"/>
-      <c r="G103" s="12" t="n"/>
-      <c r="H103" s="12" t="n"/>
+      <c r="F103" s="4" t="n"/>
+      <c r="G103" s="4" t="n"/>
+      <c r="H103" s="4" t="n"/>
       <c r="I103" s="3" t="n"/>
       <c r="J103" s="7" t="n">
         <v>15</v>
@@ -6193,21 +6211,21 @@
         <v/>
       </c>
       <c r="N103" s="3" t="n"/>
-      <c r="O103" s="12" t="n"/>
-      <c r="P103" s="12" t="n"/>
-      <c r="Q103" s="12" t="n"/>
-      <c r="R103" s="12" t="n"/>
-      <c r="S103" s="12" t="n"/>
+      <c r="O103" s="4" t="n"/>
+      <c r="P103" s="4" t="n"/>
+      <c r="Q103" s="4" t="n"/>
+      <c r="R103" s="4" t="n"/>
+      <c r="S103" s="4" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n"/>
-      <c r="B104" s="4" t="n"/>
-      <c r="C104" s="4" t="n"/>
-      <c r="D104" s="4" t="n"/>
+      <c r="B104" s="12" t="n"/>
+      <c r="C104" s="12" t="n"/>
+      <c r="D104" s="12" t="n"/>
       <c r="E104" s="3" t="n"/>
-      <c r="F104" s="4" t="n"/>
-      <c r="G104" s="4" t="n"/>
-      <c r="H104" s="4" t="n"/>
+      <c r="F104" s="12" t="n"/>
+      <c r="G104" s="12" t="n"/>
+      <c r="H104" s="12" t="n"/>
       <c r="I104" s="3" t="n"/>
       <c r="J104" s="7" t="n">
         <v>15</v>
@@ -6223,21 +6241,21 @@
         <v/>
       </c>
       <c r="N104" s="3" t="n"/>
-      <c r="O104" s="4" t="n"/>
-      <c r="P104" s="4" t="n"/>
-      <c r="Q104" s="4" t="n"/>
-      <c r="R104" s="4" t="n"/>
-      <c r="S104" s="4" t="n"/>
+      <c r="O104" s="12" t="n"/>
+      <c r="P104" s="12" t="n"/>
+      <c r="Q104" s="12" t="n"/>
+      <c r="R104" s="12" t="n"/>
+      <c r="S104" s="12" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n"/>
-      <c r="B105" s="12" t="n"/>
-      <c r="C105" s="12" t="n"/>
-      <c r="D105" s="12" t="n"/>
+      <c r="B105" s="4" t="n"/>
+      <c r="C105" s="4" t="n"/>
+      <c r="D105" s="4" t="n"/>
       <c r="E105" s="3" t="n"/>
-      <c r="F105" s="12" t="n"/>
-      <c r="G105" s="12" t="n"/>
-      <c r="H105" s="12" t="n"/>
+      <c r="F105" s="4" t="n"/>
+      <c r="G105" s="4" t="n"/>
+      <c r="H105" s="4" t="n"/>
       <c r="I105" s="3" t="n"/>
       <c r="J105" s="7" t="n">
         <v>15</v>
@@ -6253,21 +6271,21 @@
         <v/>
       </c>
       <c r="N105" s="3" t="n"/>
-      <c r="O105" s="12" t="n"/>
-      <c r="P105" s="12" t="n"/>
-      <c r="Q105" s="12" t="n"/>
-      <c r="R105" s="12" t="n"/>
-      <c r="S105" s="12" t="n"/>
+      <c r="O105" s="4" t="n"/>
+      <c r="P105" s="4" t="n"/>
+      <c r="Q105" s="4" t="n"/>
+      <c r="R105" s="4" t="n"/>
+      <c r="S105" s="4" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n"/>
-      <c r="B106" s="4" t="n"/>
-      <c r="C106" s="4" t="n"/>
-      <c r="D106" s="4" t="n"/>
+      <c r="B106" s="12" t="n"/>
+      <c r="C106" s="12" t="n"/>
+      <c r="D106" s="12" t="n"/>
       <c r="E106" s="3" t="n"/>
-      <c r="F106" s="4" t="n"/>
-      <c r="G106" s="4" t="n"/>
-      <c r="H106" s="4" t="n"/>
+      <c r="F106" s="12" t="n"/>
+      <c r="G106" s="12" t="n"/>
+      <c r="H106" s="12" t="n"/>
       <c r="I106" s="3" t="n"/>
       <c r="J106" s="7" t="n">
         <v>15</v>
@@ -6283,21 +6301,21 @@
         <v/>
       </c>
       <c r="N106" s="3" t="n"/>
-      <c r="O106" s="4" t="n"/>
-      <c r="P106" s="4" t="n"/>
-      <c r="Q106" s="4" t="n"/>
-      <c r="R106" s="4" t="n"/>
-      <c r="S106" s="4" t="n"/>
+      <c r="O106" s="12" t="n"/>
+      <c r="P106" s="12" t="n"/>
+      <c r="Q106" s="12" t="n"/>
+      <c r="R106" s="12" t="n"/>
+      <c r="S106" s="12" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n"/>
-      <c r="B107" s="12" t="n"/>
-      <c r="C107" s="12" t="n"/>
-      <c r="D107" s="12" t="n"/>
+      <c r="B107" s="4" t="n"/>
+      <c r="C107" s="4" t="n"/>
+      <c r="D107" s="4" t="n"/>
       <c r="E107" s="3" t="n"/>
-      <c r="F107" s="12" t="n"/>
-      <c r="G107" s="12" t="n"/>
-      <c r="H107" s="12" t="n"/>
+      <c r="F107" s="4" t="n"/>
+      <c r="G107" s="4" t="n"/>
+      <c r="H107" s="4" t="n"/>
       <c r="I107" s="3" t="n"/>
       <c r="J107" s="7" t="n">
         <v>15</v>
@@ -6313,21 +6331,21 @@
         <v/>
       </c>
       <c r="N107" s="3" t="n"/>
-      <c r="O107" s="12" t="n"/>
-      <c r="P107" s="12" t="n"/>
-      <c r="Q107" s="12" t="n"/>
-      <c r="R107" s="12" t="n"/>
-      <c r="S107" s="12" t="n"/>
+      <c r="O107" s="4" t="n"/>
+      <c r="P107" s="4" t="n"/>
+      <c r="Q107" s="4" t="n"/>
+      <c r="R107" s="4" t="n"/>
+      <c r="S107" s="4" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n"/>
-      <c r="B108" s="4" t="n"/>
-      <c r="C108" s="4" t="n"/>
-      <c r="D108" s="4" t="n"/>
+      <c r="B108" s="12" t="n"/>
+      <c r="C108" s="12" t="n"/>
+      <c r="D108" s="12" t="n"/>
       <c r="E108" s="3" t="n"/>
-      <c r="F108" s="4" t="n"/>
-      <c r="G108" s="4" t="n"/>
-      <c r="H108" s="4" t="n"/>
+      <c r="F108" s="12" t="n"/>
+      <c r="G108" s="12" t="n"/>
+      <c r="H108" s="12" t="n"/>
       <c r="I108" s="3" t="n"/>
       <c r="J108" s="7" t="n">
         <v>15</v>
@@ -6343,21 +6361,21 @@
         <v/>
       </c>
       <c r="N108" s="3" t="n"/>
-      <c r="O108" s="4" t="n"/>
-      <c r="P108" s="4" t="n"/>
-      <c r="Q108" s="4" t="n"/>
-      <c r="R108" s="4" t="n"/>
-      <c r="S108" s="4" t="n"/>
+      <c r="O108" s="12" t="n"/>
+      <c r="P108" s="12" t="n"/>
+      <c r="Q108" s="12" t="n"/>
+      <c r="R108" s="12" t="n"/>
+      <c r="S108" s="12" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n"/>
-      <c r="B109" s="12" t="n"/>
-      <c r="C109" s="12" t="n"/>
-      <c r="D109" s="12" t="n"/>
+      <c r="B109" s="4" t="n"/>
+      <c r="C109" s="4" t="n"/>
+      <c r="D109" s="4" t="n"/>
       <c r="E109" s="3" t="n"/>
-      <c r="F109" s="12" t="n"/>
-      <c r="G109" s="12" t="n"/>
-      <c r="H109" s="12" t="n"/>
+      <c r="F109" s="4" t="n"/>
+      <c r="G109" s="4" t="n"/>
+      <c r="H109" s="4" t="n"/>
       <c r="I109" s="3" t="n"/>
       <c r="J109" s="7" t="n">
         <v>15</v>
@@ -6373,21 +6391,21 @@
         <v/>
       </c>
       <c r="N109" s="3" t="n"/>
-      <c r="O109" s="12" t="n"/>
-      <c r="P109" s="12" t="n"/>
-      <c r="Q109" s="12" t="n"/>
-      <c r="R109" s="12" t="n"/>
-      <c r="S109" s="12" t="n"/>
+      <c r="O109" s="4" t="n"/>
+      <c r="P109" s="4" t="n"/>
+      <c r="Q109" s="4" t="n"/>
+      <c r="R109" s="4" t="n"/>
+      <c r="S109" s="4" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n"/>
-      <c r="B110" s="4" t="n"/>
-      <c r="C110" s="4" t="n"/>
-      <c r="D110" s="4" t="n"/>
+      <c r="B110" s="12" t="n"/>
+      <c r="C110" s="12" t="n"/>
+      <c r="D110" s="12" t="n"/>
       <c r="E110" s="3" t="n"/>
-      <c r="F110" s="4" t="n"/>
-      <c r="G110" s="4" t="n"/>
-      <c r="H110" s="4" t="n"/>
+      <c r="F110" s="12" t="n"/>
+      <c r="G110" s="12" t="n"/>
+      <c r="H110" s="12" t="n"/>
       <c r="I110" s="3" t="n"/>
       <c r="J110" s="7" t="n">
         <v>15</v>
@@ -6403,21 +6421,21 @@
         <v/>
       </c>
       <c r="N110" s="3" t="n"/>
-      <c r="O110" s="4" t="n"/>
-      <c r="P110" s="4" t="n"/>
-      <c r="Q110" s="4" t="n"/>
-      <c r="R110" s="4" t="n"/>
-      <c r="S110" s="4" t="n"/>
+      <c r="O110" s="12" t="n"/>
+      <c r="P110" s="12" t="n"/>
+      <c r="Q110" s="12" t="n"/>
+      <c r="R110" s="12" t="n"/>
+      <c r="S110" s="12" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n"/>
-      <c r="B111" s="12" t="n"/>
-      <c r="C111" s="12" t="n"/>
-      <c r="D111" s="12" t="n"/>
+      <c r="B111" s="4" t="n"/>
+      <c r="C111" s="4" t="n"/>
+      <c r="D111" s="4" t="n"/>
       <c r="E111" s="3" t="n"/>
-      <c r="F111" s="12" t="n"/>
-      <c r="G111" s="12" t="n"/>
-      <c r="H111" s="12" t="n"/>
+      <c r="F111" s="4" t="n"/>
+      <c r="G111" s="4" t="n"/>
+      <c r="H111" s="4" t="n"/>
       <c r="I111" s="3" t="n"/>
       <c r="J111" s="7" t="n">
         <v>15</v>
@@ -6433,21 +6451,21 @@
         <v/>
       </c>
       <c r="N111" s="3" t="n"/>
-      <c r="O111" s="12" t="n"/>
-      <c r="P111" s="12" t="n"/>
-      <c r="Q111" s="12" t="n"/>
-      <c r="R111" s="12" t="n"/>
-      <c r="S111" s="12" t="n"/>
+      <c r="O111" s="4" t="n"/>
+      <c r="P111" s="4" t="n"/>
+      <c r="Q111" s="4" t="n"/>
+      <c r="R111" s="4" t="n"/>
+      <c r="S111" s="4" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n"/>
-      <c r="B112" s="4" t="n"/>
-      <c r="C112" s="4" t="n"/>
-      <c r="D112" s="4" t="n"/>
+      <c r="B112" s="12" t="n"/>
+      <c r="C112" s="12" t="n"/>
+      <c r="D112" s="12" t="n"/>
       <c r="E112" s="3" t="n"/>
-      <c r="F112" s="4" t="n"/>
-      <c r="G112" s="4" t="n"/>
-      <c r="H112" s="4" t="n"/>
+      <c r="F112" s="12" t="n"/>
+      <c r="G112" s="12" t="n"/>
+      <c r="H112" s="12" t="n"/>
       <c r="I112" s="3" t="n"/>
       <c r="J112" s="7" t="n">
         <v>15</v>
@@ -6463,21 +6481,21 @@
         <v/>
       </c>
       <c r="N112" s="3" t="n"/>
-      <c r="O112" s="4" t="n"/>
-      <c r="P112" s="4" t="n"/>
-      <c r="Q112" s="4" t="n"/>
-      <c r="R112" s="4" t="n"/>
-      <c r="S112" s="4" t="n"/>
+      <c r="O112" s="12" t="n"/>
+      <c r="P112" s="12" t="n"/>
+      <c r="Q112" s="12" t="n"/>
+      <c r="R112" s="12" t="n"/>
+      <c r="S112" s="12" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n"/>
-      <c r="B113" s="12" t="n"/>
-      <c r="C113" s="12" t="n"/>
-      <c r="D113" s="12" t="n"/>
+      <c r="B113" s="4" t="n"/>
+      <c r="C113" s="4" t="n"/>
+      <c r="D113" s="4" t="n"/>
       <c r="E113" s="3" t="n"/>
-      <c r="F113" s="12" t="n"/>
-      <c r="G113" s="12" t="n"/>
-      <c r="H113" s="12" t="n"/>
+      <c r="F113" s="4" t="n"/>
+      <c r="G113" s="4" t="n"/>
+      <c r="H113" s="4" t="n"/>
       <c r="I113" s="3" t="n"/>
       <c r="J113" s="7" t="n">
         <v>15</v>
@@ -6493,21 +6511,21 @@
         <v/>
       </c>
       <c r="N113" s="3" t="n"/>
-      <c r="O113" s="12" t="n"/>
-      <c r="P113" s="12" t="n"/>
-      <c r="Q113" s="12" t="n"/>
-      <c r="R113" s="12" t="n"/>
-      <c r="S113" s="12" t="n"/>
+      <c r="O113" s="4" t="n"/>
+      <c r="P113" s="4" t="n"/>
+      <c r="Q113" s="4" t="n"/>
+      <c r="R113" s="4" t="n"/>
+      <c r="S113" s="4" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n"/>
-      <c r="B114" s="4" t="n"/>
-      <c r="C114" s="4" t="n"/>
-      <c r="D114" s="4" t="n"/>
+      <c r="B114" s="12" t="n"/>
+      <c r="C114" s="12" t="n"/>
+      <c r="D114" s="12" t="n"/>
       <c r="E114" s="3" t="n"/>
-      <c r="F114" s="4" t="n"/>
-      <c r="G114" s="4" t="n"/>
-      <c r="H114" s="4" t="n"/>
+      <c r="F114" s="12" t="n"/>
+      <c r="G114" s="12" t="n"/>
+      <c r="H114" s="12" t="n"/>
       <c r="I114" s="3" t="n"/>
       <c r="J114" s="7" t="n">
         <v>15</v>
@@ -6523,21 +6541,21 @@
         <v/>
       </c>
       <c r="N114" s="3" t="n"/>
-      <c r="O114" s="4" t="n"/>
-      <c r="P114" s="4" t="n"/>
-      <c r="Q114" s="4" t="n"/>
-      <c r="R114" s="4" t="n"/>
-      <c r="S114" s="4" t="n"/>
+      <c r="O114" s="12" t="n"/>
+      <c r="P114" s="12" t="n"/>
+      <c r="Q114" s="12" t="n"/>
+      <c r="R114" s="12" t="n"/>
+      <c r="S114" s="12" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n"/>
-      <c r="B115" s="12" t="n"/>
-      <c r="C115" s="12" t="n"/>
-      <c r="D115" s="12" t="n"/>
+      <c r="B115" s="4" t="n"/>
+      <c r="C115" s="4" t="n"/>
+      <c r="D115" s="4" t="n"/>
       <c r="E115" s="3" t="n"/>
-      <c r="F115" s="12" t="n"/>
-      <c r="G115" s="12" t="n"/>
-      <c r="H115" s="12" t="n"/>
+      <c r="F115" s="4" t="n"/>
+      <c r="G115" s="4" t="n"/>
+      <c r="H115" s="4" t="n"/>
       <c r="I115" s="3" t="n"/>
       <c r="J115" s="7" t="n">
         <v>15</v>
@@ -6553,21 +6571,21 @@
         <v/>
       </c>
       <c r="N115" s="3" t="n"/>
-      <c r="O115" s="12" t="n"/>
-      <c r="P115" s="12" t="n"/>
-      <c r="Q115" s="12" t="n"/>
-      <c r="R115" s="12" t="n"/>
-      <c r="S115" s="12" t="n"/>
+      <c r="O115" s="4" t="n"/>
+      <c r="P115" s="4" t="n"/>
+      <c r="Q115" s="4" t="n"/>
+      <c r="R115" s="4" t="n"/>
+      <c r="S115" s="4" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n"/>
-      <c r="B116" s="4" t="n"/>
-      <c r="C116" s="4" t="n"/>
-      <c r="D116" s="4" t="n"/>
+      <c r="B116" s="12" t="n"/>
+      <c r="C116" s="12" t="n"/>
+      <c r="D116" s="12" t="n"/>
       <c r="E116" s="3" t="n"/>
-      <c r="F116" s="4" t="n"/>
-      <c r="G116" s="4" t="n"/>
-      <c r="H116" s="4" t="n"/>
+      <c r="F116" s="12" t="n"/>
+      <c r="G116" s="12" t="n"/>
+      <c r="H116" s="12" t="n"/>
       <c r="I116" s="3" t="n"/>
       <c r="J116" s="7" t="n">
         <v>15</v>
@@ -6583,21 +6601,21 @@
         <v/>
       </c>
       <c r="N116" s="3" t="n"/>
-      <c r="O116" s="4" t="n"/>
-      <c r="P116" s="4" t="n"/>
-      <c r="Q116" s="4" t="n"/>
-      <c r="R116" s="4" t="n"/>
-      <c r="S116" s="4" t="n"/>
+      <c r="O116" s="12" t="n"/>
+      <c r="P116" s="12" t="n"/>
+      <c r="Q116" s="12" t="n"/>
+      <c r="R116" s="12" t="n"/>
+      <c r="S116" s="12" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n"/>
-      <c r="B117" s="12" t="n"/>
-      <c r="C117" s="12" t="n"/>
-      <c r="D117" s="12" t="n"/>
+      <c r="B117" s="4" t="n"/>
+      <c r="C117" s="4" t="n"/>
+      <c r="D117" s="4" t="n"/>
       <c r="E117" s="3" t="n"/>
-      <c r="F117" s="12" t="n"/>
-      <c r="G117" s="12" t="n"/>
-      <c r="H117" s="12" t="n"/>
+      <c r="F117" s="4" t="n"/>
+      <c r="G117" s="4" t="n"/>
+      <c r="H117" s="4" t="n"/>
       <c r="I117" s="3" t="n"/>
       <c r="J117" s="7" t="n">
         <v>15</v>
@@ -6613,21 +6631,21 @@
         <v/>
       </c>
       <c r="N117" s="3" t="n"/>
-      <c r="O117" s="12" t="n"/>
-      <c r="P117" s="12" t="n"/>
-      <c r="Q117" s="12" t="n"/>
-      <c r="R117" s="12" t="n"/>
-      <c r="S117" s="12" t="n"/>
+      <c r="O117" s="4" t="n"/>
+      <c r="P117" s="4" t="n"/>
+      <c r="Q117" s="4" t="n"/>
+      <c r="R117" s="4" t="n"/>
+      <c r="S117" s="4" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n"/>
-      <c r="B118" s="4" t="n"/>
-      <c r="C118" s="4" t="n"/>
-      <c r="D118" s="4" t="n"/>
+      <c r="B118" s="12" t="n"/>
+      <c r="C118" s="12" t="n"/>
+      <c r="D118" s="12" t="n"/>
       <c r="E118" s="3" t="n"/>
-      <c r="F118" s="4" t="n"/>
-      <c r="G118" s="4" t="n"/>
-      <c r="H118" s="4" t="n"/>
+      <c r="F118" s="12" t="n"/>
+      <c r="G118" s="12" t="n"/>
+      <c r="H118" s="12" t="n"/>
       <c r="I118" s="3" t="n"/>
       <c r="J118" s="7" t="n">
         <v>15</v>
@@ -6643,21 +6661,21 @@
         <v/>
       </c>
       <c r="N118" s="3" t="n"/>
-      <c r="O118" s="4" t="n"/>
-      <c r="P118" s="4" t="n"/>
-      <c r="Q118" s="4" t="n"/>
-      <c r="R118" s="4" t="n"/>
-      <c r="S118" s="4" t="n"/>
+      <c r="O118" s="12" t="n"/>
+      <c r="P118" s="12" t="n"/>
+      <c r="Q118" s="12" t="n"/>
+      <c r="R118" s="12" t="n"/>
+      <c r="S118" s="12" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n"/>
-      <c r="B119" s="12" t="n"/>
-      <c r="C119" s="12" t="n"/>
-      <c r="D119" s="12" t="n"/>
+      <c r="B119" s="4" t="n"/>
+      <c r="C119" s="4" t="n"/>
+      <c r="D119" s="4" t="n"/>
       <c r="E119" s="3" t="n"/>
-      <c r="F119" s="12" t="n"/>
-      <c r="G119" s="12" t="n"/>
-      <c r="H119" s="12" t="n"/>
+      <c r="F119" s="4" t="n"/>
+      <c r="G119" s="4" t="n"/>
+      <c r="H119" s="4" t="n"/>
       <c r="I119" s="3" t="n"/>
       <c r="J119" s="7" t="n">
         <v>15</v>
@@ -6673,21 +6691,21 @@
         <v/>
       </c>
       <c r="N119" s="3" t="n"/>
-      <c r="O119" s="12" t="n"/>
-      <c r="P119" s="12" t="n"/>
-      <c r="Q119" s="12" t="n"/>
-      <c r="R119" s="12" t="n"/>
-      <c r="S119" s="12" t="n"/>
+      <c r="O119" s="4" t="n"/>
+      <c r="P119" s="4" t="n"/>
+      <c r="Q119" s="4" t="n"/>
+      <c r="R119" s="4" t="n"/>
+      <c r="S119" s="4" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n"/>
-      <c r="B120" s="4" t="n"/>
-      <c r="C120" s="4" t="n"/>
-      <c r="D120" s="4" t="n"/>
+      <c r="B120" s="12" t="n"/>
+      <c r="C120" s="12" t="n"/>
+      <c r="D120" s="12" t="n"/>
       <c r="E120" s="3" t="n"/>
-      <c r="F120" s="4" t="n"/>
-      <c r="G120" s="4" t="n"/>
-      <c r="H120" s="4" t="n"/>
+      <c r="F120" s="12" t="n"/>
+      <c r="G120" s="12" t="n"/>
+      <c r="H120" s="12" t="n"/>
       <c r="I120" s="3" t="n"/>
       <c r="J120" s="7" t="n">
         <v>15</v>
@@ -6703,21 +6721,21 @@
         <v/>
       </c>
       <c r="N120" s="3" t="n"/>
-      <c r="O120" s="4" t="n"/>
-      <c r="P120" s="4" t="n"/>
-      <c r="Q120" s="4" t="n"/>
-      <c r="R120" s="4" t="n"/>
-      <c r="S120" s="4" t="n"/>
+      <c r="O120" s="12" t="n"/>
+      <c r="P120" s="12" t="n"/>
+      <c r="Q120" s="12" t="n"/>
+      <c r="R120" s="12" t="n"/>
+      <c r="S120" s="12" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n"/>
-      <c r="B121" s="12" t="n"/>
-      <c r="C121" s="12" t="n"/>
-      <c r="D121" s="12" t="n"/>
+      <c r="B121" s="4" t="n"/>
+      <c r="C121" s="4" t="n"/>
+      <c r="D121" s="4" t="n"/>
       <c r="E121" s="3" t="n"/>
-      <c r="F121" s="12" t="n"/>
-      <c r="G121" s="12" t="n"/>
-      <c r="H121" s="12" t="n"/>
+      <c r="F121" s="4" t="n"/>
+      <c r="G121" s="4" t="n"/>
+      <c r="H121" s="4" t="n"/>
       <c r="I121" s="3" t="n"/>
       <c r="J121" s="7" t="n">
         <v>15</v>
@@ -6733,21 +6751,21 @@
         <v/>
       </c>
       <c r="N121" s="3" t="n"/>
-      <c r="O121" s="12" t="n"/>
-      <c r="P121" s="12" t="n"/>
-      <c r="Q121" s="12" t="n"/>
-      <c r="R121" s="12" t="n"/>
-      <c r="S121" s="12" t="n"/>
+      <c r="O121" s="4" t="n"/>
+      <c r="P121" s="4" t="n"/>
+      <c r="Q121" s="4" t="n"/>
+      <c r="R121" s="4" t="n"/>
+      <c r="S121" s="4" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n"/>
-      <c r="B122" s="4" t="n"/>
-      <c r="C122" s="4" t="n"/>
-      <c r="D122" s="4" t="n"/>
+      <c r="B122" s="12" t="n"/>
+      <c r="C122" s="12" t="n"/>
+      <c r="D122" s="12" t="n"/>
       <c r="E122" s="3" t="n"/>
-      <c r="F122" s="4" t="n"/>
-      <c r="G122" s="4" t="n"/>
-      <c r="H122" s="4" t="n"/>
+      <c r="F122" s="12" t="n"/>
+      <c r="G122" s="12" t="n"/>
+      <c r="H122" s="12" t="n"/>
       <c r="I122" s="3" t="n"/>
       <c r="J122" s="7" t="n">
         <v>15</v>
@@ -6763,21 +6781,21 @@
         <v/>
       </c>
       <c r="N122" s="3" t="n"/>
-      <c r="O122" s="4" t="n"/>
-      <c r="P122" s="4" t="n"/>
-      <c r="Q122" s="4" t="n"/>
-      <c r="R122" s="4" t="n"/>
-      <c r="S122" s="4" t="n"/>
+      <c r="O122" s="12" t="n"/>
+      <c r="P122" s="12" t="n"/>
+      <c r="Q122" s="12" t="n"/>
+      <c r="R122" s="12" t="n"/>
+      <c r="S122" s="12" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n"/>
-      <c r="B123" s="12" t="n"/>
-      <c r="C123" s="12" t="n"/>
-      <c r="D123" s="12" t="n"/>
+      <c r="B123" s="4" t="n"/>
+      <c r="C123" s="4" t="n"/>
+      <c r="D123" s="4" t="n"/>
       <c r="E123" s="3" t="n"/>
-      <c r="F123" s="12" t="n"/>
-      <c r="G123" s="12" t="n"/>
-      <c r="H123" s="12" t="n"/>
+      <c r="F123" s="4" t="n"/>
+      <c r="G123" s="4" t="n"/>
+      <c r="H123" s="4" t="n"/>
       <c r="I123" s="3" t="n"/>
       <c r="J123" s="7" t="n">
         <v>15</v>
@@ -6793,21 +6811,21 @@
         <v/>
       </c>
       <c r="N123" s="3" t="n"/>
-      <c r="O123" s="12" t="n"/>
-      <c r="P123" s="12" t="n"/>
-      <c r="Q123" s="12" t="n"/>
-      <c r="R123" s="12" t="n"/>
-      <c r="S123" s="12" t="n"/>
+      <c r="O123" s="4" t="n"/>
+      <c r="P123" s="4" t="n"/>
+      <c r="Q123" s="4" t="n"/>
+      <c r="R123" s="4" t="n"/>
+      <c r="S123" s="4" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n"/>
-      <c r="B124" s="4" t="n"/>
-      <c r="C124" s="4" t="n"/>
-      <c r="D124" s="4" t="n"/>
+      <c r="B124" s="12" t="n"/>
+      <c r="C124" s="12" t="n"/>
+      <c r="D124" s="12" t="n"/>
       <c r="E124" s="3" t="n"/>
-      <c r="F124" s="4" t="n"/>
-      <c r="G124" s="4" t="n"/>
-      <c r="H124" s="4" t="n"/>
+      <c r="F124" s="12" t="n"/>
+      <c r="G124" s="12" t="n"/>
+      <c r="H124" s="12" t="n"/>
       <c r="I124" s="3" t="n"/>
       <c r="J124" s="7" t="n">
         <v>15</v>
@@ -6823,21 +6841,21 @@
         <v/>
       </c>
       <c r="N124" s="3" t="n"/>
-      <c r="O124" s="4" t="n"/>
-      <c r="P124" s="4" t="n"/>
-      <c r="Q124" s="4" t="n"/>
-      <c r="R124" s="4" t="n"/>
-      <c r="S124" s="4" t="n"/>
+      <c r="O124" s="12" t="n"/>
+      <c r="P124" s="12" t="n"/>
+      <c r="Q124" s="12" t="n"/>
+      <c r="R124" s="12" t="n"/>
+      <c r="S124" s="12" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n"/>
-      <c r="B125" s="12" t="n"/>
-      <c r="C125" s="12" t="n"/>
-      <c r="D125" s="12" t="n"/>
+      <c r="B125" s="4" t="n"/>
+      <c r="C125" s="4" t="n"/>
+      <c r="D125" s="4" t="n"/>
       <c r="E125" s="3" t="n"/>
-      <c r="F125" s="12" t="n"/>
-      <c r="G125" s="12" t="n"/>
-      <c r="H125" s="12" t="n"/>
+      <c r="F125" s="4" t="n"/>
+      <c r="G125" s="4" t="n"/>
+      <c r="H125" s="4" t="n"/>
       <c r="I125" s="3" t="n"/>
       <c r="J125" s="7" t="n">
         <v>15</v>
@@ -6853,21 +6871,21 @@
         <v/>
       </c>
       <c r="N125" s="3" t="n"/>
-      <c r="O125" s="12" t="n"/>
-      <c r="P125" s="12" t="n"/>
-      <c r="Q125" s="12" t="n"/>
-      <c r="R125" s="12" t="n"/>
-      <c r="S125" s="12" t="n"/>
+      <c r="O125" s="4" t="n"/>
+      <c r="P125" s="4" t="n"/>
+      <c r="Q125" s="4" t="n"/>
+      <c r="R125" s="4" t="n"/>
+      <c r="S125" s="4" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n"/>
-      <c r="B126" s="4" t="n"/>
-      <c r="C126" s="4" t="n"/>
-      <c r="D126" s="4" t="n"/>
+      <c r="B126" s="12" t="n"/>
+      <c r="C126" s="12" t="n"/>
+      <c r="D126" s="12" t="n"/>
       <c r="E126" s="3" t="n"/>
-      <c r="F126" s="4" t="n"/>
-      <c r="G126" s="4" t="n"/>
-      <c r="H126" s="4" t="n"/>
+      <c r="F126" s="12" t="n"/>
+      <c r="G126" s="12" t="n"/>
+      <c r="H126" s="12" t="n"/>
       <c r="I126" s="3" t="n"/>
       <c r="J126" s="7" t="n">
         <v>15</v>
@@ -6883,21 +6901,21 @@
         <v/>
       </c>
       <c r="N126" s="3" t="n"/>
-      <c r="O126" s="4" t="n"/>
-      <c r="P126" s="4" t="n"/>
-      <c r="Q126" s="4" t="n"/>
-      <c r="R126" s="4" t="n"/>
-      <c r="S126" s="4" t="n"/>
+      <c r="O126" s="12" t="n"/>
+      <c r="P126" s="12" t="n"/>
+      <c r="Q126" s="12" t="n"/>
+      <c r="R126" s="12" t="n"/>
+      <c r="S126" s="12" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n"/>
-      <c r="B127" s="12" t="n"/>
-      <c r="C127" s="12" t="n"/>
-      <c r="D127" s="12" t="n"/>
+      <c r="B127" s="4" t="n"/>
+      <c r="C127" s="4" t="n"/>
+      <c r="D127" s="4" t="n"/>
       <c r="E127" s="3" t="n"/>
-      <c r="F127" s="12" t="n"/>
-      <c r="G127" s="12" t="n"/>
-      <c r="H127" s="12" t="n"/>
+      <c r="F127" s="4" t="n"/>
+      <c r="G127" s="4" t="n"/>
+      <c r="H127" s="4" t="n"/>
       <c r="I127" s="3" t="n"/>
       <c r="J127" s="7" t="n">
         <v>15</v>
@@ -6913,21 +6931,21 @@
         <v/>
       </c>
       <c r="N127" s="3" t="n"/>
-      <c r="O127" s="12" t="n"/>
-      <c r="P127" s="12" t="n"/>
-      <c r="Q127" s="12" t="n"/>
-      <c r="R127" s="12" t="n"/>
-      <c r="S127" s="12" t="n"/>
+      <c r="O127" s="4" t="n"/>
+      <c r="P127" s="4" t="n"/>
+      <c r="Q127" s="4" t="n"/>
+      <c r="R127" s="4" t="n"/>
+      <c r="S127" s="4" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n"/>
-      <c r="B128" s="4" t="n"/>
-      <c r="C128" s="4" t="n"/>
-      <c r="D128" s="4" t="n"/>
+      <c r="B128" s="12" t="n"/>
+      <c r="C128" s="12" t="n"/>
+      <c r="D128" s="12" t="n"/>
       <c r="E128" s="3" t="n"/>
-      <c r="F128" s="4" t="n"/>
-      <c r="G128" s="4" t="n"/>
-      <c r="H128" s="4" t="n"/>
+      <c r="F128" s="12" t="n"/>
+      <c r="G128" s="12" t="n"/>
+      <c r="H128" s="12" t="n"/>
       <c r="I128" s="3" t="n"/>
       <c r="J128" s="7" t="n">
         <v>15</v>
@@ -6943,21 +6961,21 @@
         <v/>
       </c>
       <c r="N128" s="3" t="n"/>
-      <c r="O128" s="4" t="n"/>
-      <c r="P128" s="4" t="n"/>
-      <c r="Q128" s="4" t="n"/>
-      <c r="R128" s="4" t="n"/>
-      <c r="S128" s="4" t="n"/>
+      <c r="O128" s="12" t="n"/>
+      <c r="P128" s="12" t="n"/>
+      <c r="Q128" s="12" t="n"/>
+      <c r="R128" s="12" t="n"/>
+      <c r="S128" s="12" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n"/>
-      <c r="B129" s="12" t="n"/>
-      <c r="C129" s="12" t="n"/>
-      <c r="D129" s="12" t="n"/>
+      <c r="B129" s="4" t="n"/>
+      <c r="C129" s="4" t="n"/>
+      <c r="D129" s="4" t="n"/>
       <c r="E129" s="3" t="n"/>
-      <c r="F129" s="12" t="n"/>
-      <c r="G129" s="12" t="n"/>
-      <c r="H129" s="12" t="n"/>
+      <c r="F129" s="4" t="n"/>
+      <c r="G129" s="4" t="n"/>
+      <c r="H129" s="4" t="n"/>
       <c r="I129" s="3" t="n"/>
       <c r="J129" s="7" t="n">
         <v>15</v>
@@ -6973,21 +6991,21 @@
         <v/>
       </c>
       <c r="N129" s="3" t="n"/>
-      <c r="O129" s="12" t="n"/>
-      <c r="P129" s="12" t="n"/>
-      <c r="Q129" s="12" t="n"/>
-      <c r="R129" s="12" t="n"/>
-      <c r="S129" s="12" t="n"/>
+      <c r="O129" s="4" t="n"/>
+      <c r="P129" s="4" t="n"/>
+      <c r="Q129" s="4" t="n"/>
+      <c r="R129" s="4" t="n"/>
+      <c r="S129" s="4" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n"/>
-      <c r="B130" s="4" t="n"/>
-      <c r="C130" s="4" t="n"/>
-      <c r="D130" s="4" t="n"/>
+      <c r="B130" s="12" t="n"/>
+      <c r="C130" s="12" t="n"/>
+      <c r="D130" s="12" t="n"/>
       <c r="E130" s="3" t="n"/>
-      <c r="F130" s="4" t="n"/>
-      <c r="G130" s="4" t="n"/>
-      <c r="H130" s="4" t="n"/>
+      <c r="F130" s="12" t="n"/>
+      <c r="G130" s="12" t="n"/>
+      <c r="H130" s="12" t="n"/>
       <c r="I130" s="3" t="n"/>
       <c r="J130" s="7" t="n">
         <v>15</v>
@@ -7003,21 +7021,21 @@
         <v/>
       </c>
       <c r="N130" s="3" t="n"/>
-      <c r="O130" s="4" t="n"/>
-      <c r="P130" s="4" t="n"/>
-      <c r="Q130" s="4" t="n"/>
-      <c r="R130" s="4" t="n"/>
-      <c r="S130" s="4" t="n"/>
+      <c r="O130" s="12" t="n"/>
+      <c r="P130" s="12" t="n"/>
+      <c r="Q130" s="12" t="n"/>
+      <c r="R130" s="12" t="n"/>
+      <c r="S130" s="12" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n"/>
-      <c r="B131" s="12" t="n"/>
-      <c r="C131" s="12" t="n"/>
-      <c r="D131" s="12" t="n"/>
+      <c r="B131" s="4" t="n"/>
+      <c r="C131" s="4" t="n"/>
+      <c r="D131" s="4" t="n"/>
       <c r="E131" s="3" t="n"/>
-      <c r="F131" s="12" t="n"/>
-      <c r="G131" s="12" t="n"/>
-      <c r="H131" s="12" t="n"/>
+      <c r="F131" s="4" t="n"/>
+      <c r="G131" s="4" t="n"/>
+      <c r="H131" s="4" t="n"/>
       <c r="I131" s="3" t="n"/>
       <c r="J131" s="7" t="n">
         <v>15</v>
@@ -7033,21 +7051,21 @@
         <v/>
       </c>
       <c r="N131" s="3" t="n"/>
-      <c r="O131" s="12" t="n"/>
-      <c r="P131" s="12" t="n"/>
-      <c r="Q131" s="12" t="n"/>
-      <c r="R131" s="12" t="n"/>
-      <c r="S131" s="12" t="n"/>
+      <c r="O131" s="4" t="n"/>
+      <c r="P131" s="4" t="n"/>
+      <c r="Q131" s="4" t="n"/>
+      <c r="R131" s="4" t="n"/>
+      <c r="S131" s="4" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n"/>
-      <c r="B132" s="4" t="n"/>
-      <c r="C132" s="4" t="n"/>
-      <c r="D132" s="4" t="n"/>
+      <c r="B132" s="12" t="n"/>
+      <c r="C132" s="12" t="n"/>
+      <c r="D132" s="12" t="n"/>
       <c r="E132" s="3" t="n"/>
-      <c r="F132" s="4" t="n"/>
-      <c r="G132" s="4" t="n"/>
-      <c r="H132" s="4" t="n"/>
+      <c r="F132" s="12" t="n"/>
+      <c r="G132" s="12" t="n"/>
+      <c r="H132" s="12" t="n"/>
       <c r="I132" s="3" t="n"/>
       <c r="J132" s="7" t="n">
         <v>15</v>
@@ -7063,21 +7081,21 @@
         <v/>
       </c>
       <c r="N132" s="3" t="n"/>
-      <c r="O132" s="4" t="n"/>
-      <c r="P132" s="4" t="n"/>
-      <c r="Q132" s="4" t="n"/>
-      <c r="R132" s="4" t="n"/>
-      <c r="S132" s="4" t="n"/>
+      <c r="O132" s="12" t="n"/>
+      <c r="P132" s="12" t="n"/>
+      <c r="Q132" s="12" t="n"/>
+      <c r="R132" s="12" t="n"/>
+      <c r="S132" s="12" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n"/>
-      <c r="B133" s="12" t="n"/>
-      <c r="C133" s="12" t="n"/>
-      <c r="D133" s="12" t="n"/>
+      <c r="B133" s="4" t="n"/>
+      <c r="C133" s="4" t="n"/>
+      <c r="D133" s="4" t="n"/>
       <c r="E133" s="3" t="n"/>
-      <c r="F133" s="12" t="n"/>
-      <c r="G133" s="12" t="n"/>
-      <c r="H133" s="12" t="n"/>
+      <c r="F133" s="4" t="n"/>
+      <c r="G133" s="4" t="n"/>
+      <c r="H133" s="4" t="n"/>
       <c r="I133" s="3" t="n"/>
       <c r="J133" s="7" t="n">
         <v>15</v>
@@ -7093,21 +7111,21 @@
         <v/>
       </c>
       <c r="N133" s="3" t="n"/>
-      <c r="O133" s="12" t="n"/>
-      <c r="P133" s="12" t="n"/>
-      <c r="Q133" s="12" t="n"/>
-      <c r="R133" s="12" t="n"/>
-      <c r="S133" s="12" t="n"/>
+      <c r="O133" s="4" t="n"/>
+      <c r="P133" s="4" t="n"/>
+      <c r="Q133" s="4" t="n"/>
+      <c r="R133" s="4" t="n"/>
+      <c r="S133" s="4" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n"/>
-      <c r="B134" s="4" t="n"/>
-      <c r="C134" s="4" t="n"/>
-      <c r="D134" s="4" t="n"/>
+      <c r="B134" s="12" t="n"/>
+      <c r="C134" s="12" t="n"/>
+      <c r="D134" s="12" t="n"/>
       <c r="E134" s="3" t="n"/>
-      <c r="F134" s="4" t="n"/>
-      <c r="G134" s="4" t="n"/>
-      <c r="H134" s="4" t="n"/>
+      <c r="F134" s="12" t="n"/>
+      <c r="G134" s="12" t="n"/>
+      <c r="H134" s="12" t="n"/>
       <c r="I134" s="3" t="n"/>
       <c r="J134" s="7" t="n">
         <v>15</v>
@@ -7123,21 +7141,21 @@
         <v/>
       </c>
       <c r="N134" s="3" t="n"/>
-      <c r="O134" s="4" t="n"/>
-      <c r="P134" s="4" t="n"/>
-      <c r="Q134" s="4" t="n"/>
-      <c r="R134" s="4" t="n"/>
-      <c r="S134" s="4" t="n"/>
+      <c r="O134" s="12" t="n"/>
+      <c r="P134" s="12" t="n"/>
+      <c r="Q134" s="12" t="n"/>
+      <c r="R134" s="12" t="n"/>
+      <c r="S134" s="12" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n"/>
-      <c r="B135" s="12" t="n"/>
-      <c r="C135" s="12" t="n"/>
-      <c r="D135" s="12" t="n"/>
+      <c r="B135" s="4" t="n"/>
+      <c r="C135" s="4" t="n"/>
+      <c r="D135" s="4" t="n"/>
       <c r="E135" s="3" t="n"/>
-      <c r="F135" s="12" t="n"/>
-      <c r="G135" s="12" t="n"/>
-      <c r="H135" s="12" t="n"/>
+      <c r="F135" s="4" t="n"/>
+      <c r="G135" s="4" t="n"/>
+      <c r="H135" s="4" t="n"/>
       <c r="I135" s="3" t="n"/>
       <c r="J135" s="7" t="n">
         <v>15</v>
@@ -7153,21 +7171,21 @@
         <v/>
       </c>
       <c r="N135" s="3" t="n"/>
-      <c r="O135" s="12" t="n"/>
-      <c r="P135" s="12" t="n"/>
-      <c r="Q135" s="12" t="n"/>
-      <c r="R135" s="12" t="n"/>
-      <c r="S135" s="12" t="n"/>
+      <c r="O135" s="4" t="n"/>
+      <c r="P135" s="4" t="n"/>
+      <c r="Q135" s="4" t="n"/>
+      <c r="R135" s="4" t="n"/>
+      <c r="S135" s="4" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n"/>
-      <c r="B136" s="4" t="n"/>
-      <c r="C136" s="4" t="n"/>
-      <c r="D136" s="4" t="n"/>
+      <c r="B136" s="12" t="n"/>
+      <c r="C136" s="12" t="n"/>
+      <c r="D136" s="12" t="n"/>
       <c r="E136" s="3" t="n"/>
-      <c r="F136" s="4" t="n"/>
-      <c r="G136" s="4" t="n"/>
-      <c r="H136" s="4" t="n"/>
+      <c r="F136" s="12" t="n"/>
+      <c r="G136" s="12" t="n"/>
+      <c r="H136" s="12" t="n"/>
       <c r="I136" s="3" t="n"/>
       <c r="J136" s="7" t="n">
         <v>15</v>
@@ -7183,21 +7201,21 @@
         <v/>
       </c>
       <c r="N136" s="3" t="n"/>
-      <c r="O136" s="4" t="n"/>
-      <c r="P136" s="4" t="n"/>
-      <c r="Q136" s="4" t="n"/>
-      <c r="R136" s="4" t="n"/>
-      <c r="S136" s="4" t="n"/>
+      <c r="O136" s="12" t="n"/>
+      <c r="P136" s="12" t="n"/>
+      <c r="Q136" s="12" t="n"/>
+      <c r="R136" s="12" t="n"/>
+      <c r="S136" s="12" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n"/>
-      <c r="B137" s="12" t="n"/>
-      <c r="C137" s="12" t="n"/>
-      <c r="D137" s="12" t="n"/>
+      <c r="B137" s="4" t="n"/>
+      <c r="C137" s="4" t="n"/>
+      <c r="D137" s="4" t="n"/>
       <c r="E137" s="3" t="n"/>
-      <c r="F137" s="12" t="n"/>
-      <c r="G137" s="12" t="n"/>
-      <c r="H137" s="12" t="n"/>
+      <c r="F137" s="4" t="n"/>
+      <c r="G137" s="4" t="n"/>
+      <c r="H137" s="4" t="n"/>
       <c r="I137" s="3" t="n"/>
       <c r="J137" s="7" t="n">
         <v>15</v>
@@ -7213,21 +7231,21 @@
         <v/>
       </c>
       <c r="N137" s="3" t="n"/>
-      <c r="O137" s="12" t="n"/>
-      <c r="P137" s="12" t="n"/>
-      <c r="Q137" s="12" t="n"/>
-      <c r="R137" s="12" t="n"/>
-      <c r="S137" s="12" t="n"/>
+      <c r="O137" s="4" t="n"/>
+      <c r="P137" s="4" t="n"/>
+      <c r="Q137" s="4" t="n"/>
+      <c r="R137" s="4" t="n"/>
+      <c r="S137" s="4" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n"/>
-      <c r="B138" s="4" t="n"/>
-      <c r="C138" s="4" t="n"/>
-      <c r="D138" s="4" t="n"/>
+      <c r="B138" s="12" t="n"/>
+      <c r="C138" s="12" t="n"/>
+      <c r="D138" s="12" t="n"/>
       <c r="E138" s="3" t="n"/>
-      <c r="F138" s="4" t="n"/>
-      <c r="G138" s="4" t="n"/>
-      <c r="H138" s="4" t="n"/>
+      <c r="F138" s="12" t="n"/>
+      <c r="G138" s="12" t="n"/>
+      <c r="H138" s="12" t="n"/>
       <c r="I138" s="3" t="n"/>
       <c r="J138" s="7" t="n">
         <v>15</v>
@@ -7243,21 +7261,21 @@
         <v/>
       </c>
       <c r="N138" s="3" t="n"/>
-      <c r="O138" s="4" t="n"/>
-      <c r="P138" s="4" t="n"/>
-      <c r="Q138" s="4" t="n"/>
-      <c r="R138" s="4" t="n"/>
-      <c r="S138" s="4" t="n"/>
+      <c r="O138" s="12" t="n"/>
+      <c r="P138" s="12" t="n"/>
+      <c r="Q138" s="12" t="n"/>
+      <c r="R138" s="12" t="n"/>
+      <c r="S138" s="12" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n"/>
-      <c r="B139" s="12" t="n"/>
-      <c r="C139" s="12" t="n"/>
-      <c r="D139" s="12" t="n"/>
+      <c r="B139" s="4" t="n"/>
+      <c r="C139" s="4" t="n"/>
+      <c r="D139" s="4" t="n"/>
       <c r="E139" s="3" t="n"/>
-      <c r="F139" s="12" t="n"/>
-      <c r="G139" s="12" t="n"/>
-      <c r="H139" s="12" t="n"/>
+      <c r="F139" s="4" t="n"/>
+      <c r="G139" s="4" t="n"/>
+      <c r="H139" s="4" t="n"/>
       <c r="I139" s="3" t="n"/>
       <c r="J139" s="7" t="n">
         <v>15</v>
@@ -7273,21 +7291,21 @@
         <v/>
       </c>
       <c r="N139" s="3" t="n"/>
-      <c r="O139" s="12" t="n"/>
-      <c r="P139" s="12" t="n"/>
-      <c r="Q139" s="12" t="n"/>
-      <c r="R139" s="12" t="n"/>
-      <c r="S139" s="12" t="n"/>
+      <c r="O139" s="4" t="n"/>
+      <c r="P139" s="4" t="n"/>
+      <c r="Q139" s="4" t="n"/>
+      <c r="R139" s="4" t="n"/>
+      <c r="S139" s="4" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n"/>
-      <c r="B140" s="4" t="n"/>
-      <c r="C140" s="4" t="n"/>
-      <c r="D140" s="4" t="n"/>
+      <c r="B140" s="12" t="n"/>
+      <c r="C140" s="12" t="n"/>
+      <c r="D140" s="12" t="n"/>
       <c r="E140" s="3" t="n"/>
-      <c r="F140" s="4" t="n"/>
-      <c r="G140" s="4" t="n"/>
-      <c r="H140" s="4" t="n"/>
+      <c r="F140" s="12" t="n"/>
+      <c r="G140" s="12" t="n"/>
+      <c r="H140" s="12" t="n"/>
       <c r="I140" s="3" t="n"/>
       <c r="J140" s="7" t="n">
         <v>15</v>
@@ -7303,21 +7321,21 @@
         <v/>
       </c>
       <c r="N140" s="3" t="n"/>
-      <c r="O140" s="4" t="n"/>
-      <c r="P140" s="4" t="n"/>
-      <c r="Q140" s="4" t="n"/>
-      <c r="R140" s="4" t="n"/>
-      <c r="S140" s="4" t="n"/>
+      <c r="O140" s="12" t="n"/>
+      <c r="P140" s="12" t="n"/>
+      <c r="Q140" s="12" t="n"/>
+      <c r="R140" s="12" t="n"/>
+      <c r="S140" s="12" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n"/>
-      <c r="B141" s="12" t="n"/>
-      <c r="C141" s="12" t="n"/>
-      <c r="D141" s="12" t="n"/>
+      <c r="B141" s="4" t="n"/>
+      <c r="C141" s="4" t="n"/>
+      <c r="D141" s="4" t="n"/>
       <c r="E141" s="3" t="n"/>
-      <c r="F141" s="12" t="n"/>
-      <c r="G141" s="12" t="n"/>
-      <c r="H141" s="12" t="n"/>
+      <c r="F141" s="4" t="n"/>
+      <c r="G141" s="4" t="n"/>
+      <c r="H141" s="4" t="n"/>
       <c r="I141" s="3" t="n"/>
       <c r="J141" s="7" t="n">
         <v>15</v>
@@ -7333,21 +7351,21 @@
         <v/>
       </c>
       <c r="N141" s="3" t="n"/>
-      <c r="O141" s="12" t="n"/>
-      <c r="P141" s="12" t="n"/>
-      <c r="Q141" s="12" t="n"/>
-      <c r="R141" s="12" t="n"/>
-      <c r="S141" s="12" t="n"/>
+      <c r="O141" s="4" t="n"/>
+      <c r="P141" s="4" t="n"/>
+      <c r="Q141" s="4" t="n"/>
+      <c r="R141" s="4" t="n"/>
+      <c r="S141" s="4" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n"/>
-      <c r="B142" s="4" t="n"/>
-      <c r="C142" s="4" t="n"/>
-      <c r="D142" s="4" t="n"/>
+      <c r="B142" s="12" t="n"/>
+      <c r="C142" s="12" t="n"/>
+      <c r="D142" s="12" t="n"/>
       <c r="E142" s="3" t="n"/>
-      <c r="F142" s="4" t="n"/>
-      <c r="G142" s="4" t="n"/>
-      <c r="H142" s="4" t="n"/>
+      <c r="F142" s="12" t="n"/>
+      <c r="G142" s="12" t="n"/>
+      <c r="H142" s="12" t="n"/>
       <c r="I142" s="3" t="n"/>
       <c r="J142" s="7" t="n">
         <v>15</v>
@@ -7363,21 +7381,21 @@
         <v/>
       </c>
       <c r="N142" s="3" t="n"/>
-      <c r="O142" s="4" t="n"/>
-      <c r="P142" s="4" t="n"/>
-      <c r="Q142" s="4" t="n"/>
-      <c r="R142" s="4" t="n"/>
-      <c r="S142" s="4" t="n"/>
+      <c r="O142" s="12" t="n"/>
+      <c r="P142" s="12" t="n"/>
+      <c r="Q142" s="12" t="n"/>
+      <c r="R142" s="12" t="n"/>
+      <c r="S142" s="12" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n"/>
-      <c r="B143" s="12" t="n"/>
-      <c r="C143" s="12" t="n"/>
-      <c r="D143" s="12" t="n"/>
+      <c r="B143" s="4" t="n"/>
+      <c r="C143" s="4" t="n"/>
+      <c r="D143" s="4" t="n"/>
       <c r="E143" s="3" t="n"/>
-      <c r="F143" s="12" t="n"/>
-      <c r="G143" s="12" t="n"/>
-      <c r="H143" s="12" t="n"/>
+      <c r="F143" s="4" t="n"/>
+      <c r="G143" s="4" t="n"/>
+      <c r="H143" s="4" t="n"/>
       <c r="I143" s="3" t="n"/>
       <c r="J143" s="7" t="n">
         <v>15</v>
@@ -7393,11 +7411,221 @@
         <v/>
       </c>
       <c r="N143" s="3" t="n"/>
-      <c r="O143" s="12" t="n"/>
-      <c r="P143" s="12" t="n"/>
-      <c r="Q143" s="12" t="n"/>
-      <c r="R143" s="12" t="n"/>
-      <c r="S143" s="12" t="n"/>
+      <c r="O143" s="4" t="n"/>
+      <c r="P143" s="4" t="n"/>
+      <c r="Q143" s="4" t="n"/>
+      <c r="R143" s="4" t="n"/>
+      <c r="S143" s="4" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="n"/>
+      <c r="B144" s="12" t="n"/>
+      <c r="C144" s="12" t="n"/>
+      <c r="D144" s="12" t="n"/>
+      <c r="E144" s="3" t="n"/>
+      <c r="F144" s="12" t="n"/>
+      <c r="G144" s="12" t="n"/>
+      <c r="H144" s="12" t="n"/>
+      <c r="I144" s="3" t="n"/>
+      <c r="J144" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="K144" s="8">
+        <f>IF(I144="","",I144*(1+J144/100))</f>
+        <v/>
+      </c>
+      <c r="L144" s="3" t="n"/>
+      <c r="M144" s="10">
+        <f>IF(OR(L144="",K144="",L144=0),"",
+  (L144-K144)/L144*100)</f>
+        <v/>
+      </c>
+      <c r="N144" s="3" t="n"/>
+      <c r="O144" s="12" t="n"/>
+      <c r="P144" s="12" t="n"/>
+      <c r="Q144" s="12" t="n"/>
+      <c r="R144" s="12" t="n"/>
+      <c r="S144" s="12" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="n"/>
+      <c r="B145" s="4" t="n"/>
+      <c r="C145" s="4" t="n"/>
+      <c r="D145" s="4" t="n"/>
+      <c r="E145" s="3" t="n"/>
+      <c r="F145" s="4" t="n"/>
+      <c r="G145" s="4" t="n"/>
+      <c r="H145" s="4" t="n"/>
+      <c r="I145" s="3" t="n"/>
+      <c r="J145" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="K145" s="8">
+        <f>IF(I145="","",I145*(1+J145/100))</f>
+        <v/>
+      </c>
+      <c r="L145" s="3" t="n"/>
+      <c r="M145" s="10">
+        <f>IF(OR(L145="",K145="",L145=0),"",
+  (L145-K145)/L145*100)</f>
+        <v/>
+      </c>
+      <c r="N145" s="3" t="n"/>
+      <c r="O145" s="4" t="n"/>
+      <c r="P145" s="4" t="n"/>
+      <c r="Q145" s="4" t="n"/>
+      <c r="R145" s="4" t="n"/>
+      <c r="S145" s="4" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="n"/>
+      <c r="B146" s="12" t="n"/>
+      <c r="C146" s="12" t="n"/>
+      <c r="D146" s="12" t="n"/>
+      <c r="E146" s="3" t="n"/>
+      <c r="F146" s="12" t="n"/>
+      <c r="G146" s="12" t="n"/>
+      <c r="H146" s="12" t="n"/>
+      <c r="I146" s="3" t="n"/>
+      <c r="J146" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="K146" s="8">
+        <f>IF(I146="","",I146*(1+J146/100))</f>
+        <v/>
+      </c>
+      <c r="L146" s="3" t="n"/>
+      <c r="M146" s="10">
+        <f>IF(OR(L146="",K146="",L146=0),"",
+  (L146-K146)/L146*100)</f>
+        <v/>
+      </c>
+      <c r="N146" s="3" t="n"/>
+      <c r="O146" s="12" t="n"/>
+      <c r="P146" s="12" t="n"/>
+      <c r="Q146" s="12" t="n"/>
+      <c r="R146" s="12" t="n"/>
+      <c r="S146" s="12" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="n"/>
+      <c r="B147" s="4" t="n"/>
+      <c r="C147" s="4" t="n"/>
+      <c r="D147" s="4" t="n"/>
+      <c r="E147" s="3" t="n"/>
+      <c r="F147" s="4" t="n"/>
+      <c r="G147" s="4" t="n"/>
+      <c r="H147" s="4" t="n"/>
+      <c r="I147" s="3" t="n"/>
+      <c r="J147" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="K147" s="8">
+        <f>IF(I147="","",I147*(1+J147/100))</f>
+        <v/>
+      </c>
+      <c r="L147" s="3" t="n"/>
+      <c r="M147" s="10">
+        <f>IF(OR(L147="",K147="",L147=0),"",
+  (L147-K147)/L147*100)</f>
+        <v/>
+      </c>
+      <c r="N147" s="3" t="n"/>
+      <c r="O147" s="4" t="n"/>
+      <c r="P147" s="4" t="n"/>
+      <c r="Q147" s="4" t="n"/>
+      <c r="R147" s="4" t="n"/>
+      <c r="S147" s="4" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="n"/>
+      <c r="B148" s="12" t="n"/>
+      <c r="C148" s="12" t="n"/>
+      <c r="D148" s="12" t="n"/>
+      <c r="E148" s="3" t="n"/>
+      <c r="F148" s="12" t="n"/>
+      <c r="G148" s="12" t="n"/>
+      <c r="H148" s="12" t="n"/>
+      <c r="I148" s="3" t="n"/>
+      <c r="J148" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="K148" s="8">
+        <f>IF(I148="","",I148*(1+J148/100))</f>
+        <v/>
+      </c>
+      <c r="L148" s="3" t="n"/>
+      <c r="M148" s="10">
+        <f>IF(OR(L148="",K148="",L148=0),"",
+  (L148-K148)/L148*100)</f>
+        <v/>
+      </c>
+      <c r="N148" s="3" t="n"/>
+      <c r="O148" s="12" t="n"/>
+      <c r="P148" s="12" t="n"/>
+      <c r="Q148" s="12" t="n"/>
+      <c r="R148" s="12" t="n"/>
+      <c r="S148" s="12" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="n"/>
+      <c r="B149" s="4" t="n"/>
+      <c r="C149" s="4" t="n"/>
+      <c r="D149" s="4" t="n"/>
+      <c r="E149" s="3" t="n"/>
+      <c r="F149" s="4" t="n"/>
+      <c r="G149" s="4" t="n"/>
+      <c r="H149" s="4" t="n"/>
+      <c r="I149" s="3" t="n"/>
+      <c r="J149" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="K149" s="8">
+        <f>IF(I149="","",I149*(1+J149/100))</f>
+        <v/>
+      </c>
+      <c r="L149" s="3" t="n"/>
+      <c r="M149" s="10">
+        <f>IF(OR(L149="",K149="",L149=0),"",
+  (L149-K149)/L149*100)</f>
+        <v/>
+      </c>
+      <c r="N149" s="3" t="n"/>
+      <c r="O149" s="4" t="n"/>
+      <c r="P149" s="4" t="n"/>
+      <c r="Q149" s="4" t="n"/>
+      <c r="R149" s="4" t="n"/>
+      <c r="S149" s="4" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="n"/>
+      <c r="B150" s="12" t="n"/>
+      <c r="C150" s="12" t="n"/>
+      <c r="D150" s="12" t="n"/>
+      <c r="E150" s="3" t="n"/>
+      <c r="F150" s="12" t="n"/>
+      <c r="G150" s="12" t="n"/>
+      <c r="H150" s="12" t="n"/>
+      <c r="I150" s="3" t="n"/>
+      <c r="J150" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="K150" s="8">
+        <f>IF(I150="","",I150*(1+J150/100))</f>
+        <v/>
+      </c>
+      <c r="L150" s="3" t="n"/>
+      <c r="M150" s="10">
+        <f>IF(OR(L150="",K150="",L150=0),"",
+  (L150-K150)/L150*100)</f>
+        <v/>
+      </c>
+      <c r="N150" s="3" t="n"/>
+      <c r="O150" s="12" t="n"/>
+      <c r="P150" s="12" t="n"/>
+      <c r="Q150" s="12" t="n"/>
+      <c r="R150" s="12" t="n"/>
+      <c r="S150" s="12" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:S2"/>
